--- a/tabela_completa.xlsx
+++ b/tabela_completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="285">
   <si>
     <t>situacao</t>
   </si>
@@ -43,9 +43,6 @@
     <t>objeto_completo</t>
   </si>
   <si>
-    <t>vigencia</t>
-  </si>
-  <si>
     <t>uasg</t>
   </si>
   <si>
@@ -58,100 +55,823 @@
     <t>setor_responsavel</t>
   </si>
   <si>
-    <t>data_sessao</t>
-  </si>
-  <si>
-    <t>agente_contratacao</t>
-  </si>
-  <si>
-    <t>criterio_julgamento</t>
-  </si>
-  <si>
-    <t>atividade_custeio</t>
-  </si>
-  <si>
-    <t>previsao_contratacao</t>
-  </si>
-  <si>
-    <t>coordenador_planejamento</t>
-  </si>
-  <si>
-    <t>ordenador_despesas</t>
-  </si>
-  <si>
-    <t>agente_fiscal</t>
-  </si>
-  <si>
-    <t>gerente_de_credito</t>
-  </si>
-  <si>
-    <t>justificativa</t>
-  </si>
-  <si>
-    <t>cep</t>
-  </si>
-  <si>
-    <t>endereco</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>telefone</t>
-  </si>
-  <si>
-    <t>dias_para_recebimento</t>
-  </si>
-  <si>
-    <t>horario_para_recebimento</t>
+    <t>valor_total</t>
   </si>
   <si>
     <t>srp</t>
   </si>
   <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>Sessão Pública</t>
+  </si>
+  <si>
     <t>Planejamento</t>
   </si>
   <si>
-    <t>PE 1/2024</t>
-  </si>
-  <si>
-    <t>PE 2/2024</t>
-  </si>
-  <si>
-    <t>Pregão Eletrônico</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>Concluído</t>
+  </si>
+  <si>
+    <t>PE 07/2023</t>
+  </si>
+  <si>
+    <t>PE 08/2023</t>
+  </si>
+  <si>
+    <t>PE 10/2023</t>
+  </si>
+  <si>
+    <t>PE 90005/2024</t>
+  </si>
+  <si>
+    <t>PE 90009/2024</t>
+  </si>
+  <si>
+    <t>PE 04/2023</t>
+  </si>
+  <si>
+    <t>PE 13/2023</t>
+  </si>
+  <si>
+    <t>PE 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90002/2024</t>
+  </si>
+  <si>
+    <t>PE 90007/2024</t>
+  </si>
+  <si>
+    <t>PE 90008/2024</t>
+  </si>
+  <si>
+    <t>PE 90010/2024</t>
+  </si>
+  <si>
+    <t>PE 90011/2024</t>
+  </si>
+  <si>
+    <t>PE 90012/2024</t>
+  </si>
+  <si>
+    <t>PE 90013/2024</t>
+  </si>
+  <si>
+    <t>PE 90014/2024</t>
+  </si>
+  <si>
+    <t>PE 90015/2024</t>
+  </si>
+  <si>
+    <t>PE 90016/2024</t>
+  </si>
+  <si>
+    <t>PE 90017/2024</t>
+  </si>
+  <si>
+    <t>PE 90018/2024</t>
+  </si>
+  <si>
+    <t>PE 90019/2024</t>
+  </si>
+  <si>
+    <t>PE 90020/2024</t>
+  </si>
+  <si>
+    <t>PE 90021/2024</t>
+  </si>
+  <si>
+    <t>PE 90022/2024</t>
+  </si>
+  <si>
+    <t>PE 90023/2024</t>
+  </si>
+  <si>
+    <t>PE 90024/2024</t>
+  </si>
+  <si>
+    <t>PE 90025/2024</t>
+  </si>
+  <si>
+    <t>PE 90026/2024</t>
+  </si>
+  <si>
+    <t>PE 90027/2024</t>
+  </si>
+  <si>
+    <t>PE 90028/2024</t>
+  </si>
+  <si>
+    <t>PE 90029/2024</t>
+  </si>
+  <si>
+    <t>PE 90030/2024</t>
+  </si>
+  <si>
+    <t>PE 90031/2024</t>
+  </si>
+  <si>
+    <t>PE 90032/2024</t>
+  </si>
+  <si>
+    <t>PE 90033/2024</t>
+  </si>
+  <si>
+    <t>PE 90044/2024</t>
+  </si>
+  <si>
+    <t>TJDL 90001/2024</t>
+  </si>
+  <si>
+    <t>TJIL 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90035/2024</t>
+  </si>
+  <si>
+    <t>PE 90036/2024</t>
+  </si>
+  <si>
+    <t>PE 90037/2024</t>
+  </si>
+  <si>
+    <t>PE 90038/2024</t>
+  </si>
+  <si>
+    <t>PE 90039/2024</t>
+  </si>
+  <si>
+    <t>PE 90040/2024</t>
+  </si>
+  <si>
+    <t>PE 90041/2024</t>
+  </si>
+  <si>
+    <t>CC 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90003/2024</t>
+  </si>
+  <si>
+    <t>PE 90004/2024</t>
+  </si>
+  <si>
+    <t>PE 90006/2024</t>
+  </si>
+  <si>
+    <t>Tipo Desconhecido</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>90005</t>
+  </si>
+  <si>
+    <t>90009</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>90001</t>
+  </si>
+  <si>
+    <t>90002</t>
+  </si>
+  <si>
+    <t>90007</t>
+  </si>
+  <si>
+    <t>90008</t>
+  </si>
+  <si>
+    <t>90010</t>
+  </si>
+  <si>
+    <t>90011</t>
+  </si>
+  <si>
+    <t>90012</t>
+  </si>
+  <si>
+    <t>90013</t>
+  </si>
+  <si>
+    <t>90014</t>
+  </si>
+  <si>
+    <t>90015</t>
+  </si>
+  <si>
+    <t>90016</t>
+  </si>
+  <si>
+    <t>90017</t>
+  </si>
+  <si>
+    <t>90018</t>
+  </si>
+  <si>
+    <t>90019</t>
+  </si>
+  <si>
+    <t>90020</t>
+  </si>
+  <si>
+    <t>90021</t>
+  </si>
+  <si>
+    <t>90022</t>
+  </si>
+  <si>
+    <t>90023</t>
+  </si>
+  <si>
+    <t>90024</t>
+  </si>
+  <si>
+    <t>90025</t>
+  </si>
+  <si>
+    <t>90026</t>
+  </si>
+  <si>
+    <t>90027</t>
+  </si>
+  <si>
+    <t>90028</t>
+  </si>
+  <si>
+    <t>90029</t>
+  </si>
+  <si>
+    <t>90030</t>
+  </si>
+  <si>
+    <t>90031</t>
+  </si>
+  <si>
+    <t>90032</t>
+  </si>
+  <si>
+    <t>90033</t>
+  </si>
+  <si>
+    <t>90044</t>
+  </si>
+  <si>
+    <t>90035</t>
+  </si>
+  <si>
+    <t>90036</t>
+  </si>
+  <si>
+    <t>90037</t>
+  </si>
+  <si>
+    <t>90038</t>
+  </si>
+  <si>
+    <t>90039</t>
+  </si>
+  <si>
+    <t>90040</t>
+  </si>
+  <si>
+    <t>90041</t>
+  </si>
+  <si>
+    <t>90003</t>
+  </si>
+  <si>
+    <t>90004</t>
+  </si>
+  <si>
+    <t>90006</t>
+  </si>
+  <si>
+    <t>2023</t>
   </si>
   <si>
     <t>2024</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>Material</t>
+    <t>62055.002424/2023-25</t>
+  </si>
+  <si>
+    <t>62055.002426/2023-14</t>
+  </si>
+  <si>
+    <t>63402.000330/2024-78</t>
+  </si>
+  <si>
+    <t>63402.000313/2024-31</t>
+  </si>
+  <si>
+    <t>62055.000344/2023-35</t>
+  </si>
+  <si>
+    <t>62055.002463/2023-22</t>
+  </si>
+  <si>
+    <t>63402.000338/2024-34</t>
+  </si>
+  <si>
+    <t>63402.000331/2024-12</t>
+  </si>
+  <si>
+    <t>63402.000318/2024-63</t>
+  </si>
+  <si>
+    <t>63402.000314/2024-85</t>
+  </si>
+  <si>
+    <t>63402.000326/2024-18</t>
+  </si>
+  <si>
+    <t>63402.000286/2024-04</t>
+  </si>
+  <si>
+    <t>63402.000289/2024-30</t>
+  </si>
+  <si>
+    <t>63402.000315/2024-20</t>
+  </si>
+  <si>
+    <t>63402.000316/2024-74</t>
+  </si>
+  <si>
+    <t>63402.000319/2024-16</t>
+  </si>
+  <si>
+    <t>63402.000317/2024-19</t>
+  </si>
+  <si>
+    <t>63402.000352/2024-38</t>
+  </si>
+  <si>
+    <t>63402.000360/2024-84</t>
+  </si>
+  <si>
+    <t>63402.000359/2024-50</t>
+  </si>
+  <si>
+    <t>63402.000358/2024-13</t>
+  </si>
+  <si>
+    <t>63402.000357/2024-61</t>
+  </si>
+  <si>
+    <t>63402.000355/2024-71</t>
+  </si>
+  <si>
+    <t>63402.000354/2024-27</t>
+  </si>
+  <si>
+    <t>63402.000361/2024-69</t>
+  </si>
+  <si>
+    <t>63402.000325/2024-65</t>
+  </si>
+  <si>
+    <t>63402.000324/2024-11</t>
+  </si>
+  <si>
+    <t>63402.000321/2024-87</t>
+  </si>
+  <si>
+    <t>63402.000333/2024-10</t>
+  </si>
+  <si>
+    <t>63402.000320/2024-32</t>
+  </si>
+  <si>
+    <t>63402.000332/2024-67</t>
+  </si>
+  <si>
+    <t>63402.000322/2024-21</t>
+  </si>
+  <si>
+    <t>63402.000362/2024-73</t>
+  </si>
+  <si>
+    <t>63402.000327/2024-54</t>
+  </si>
+  <si>
+    <t>63402.000403/2024-21</t>
+  </si>
+  <si>
+    <t>62055.000130/2024-40</t>
+  </si>
+  <si>
+    <t>63402.000702/2024-66</t>
+  </si>
+  <si>
+    <t>63402.000750/2024-54</t>
+  </si>
+  <si>
+    <t>63402.000766/2024-67</t>
+  </si>
+  <si>
+    <t>63402.000881/2024-31</t>
+  </si>
+  <si>
+    <t>63402.000907/2024-41</t>
+  </si>
+  <si>
+    <t>63402.000915/2024-98</t>
+  </si>
+  <si>
+    <t>63402.001090/2024-29</t>
+  </si>
+  <si>
+    <t>63402.000800/2024-01</t>
+  </si>
+  <si>
+    <t>63402.000312/2024-96</t>
+  </si>
+  <si>
+    <t>63402.000334/2024-56</t>
+  </si>
+  <si>
+    <t>63402.000328/2024-07</t>
+  </si>
+  <si>
+    <t>material</t>
+  </si>
+  <si>
+    <t>servico</t>
   </si>
   <si>
     <t>Serviço</t>
   </si>
   <si>
-    <t>teste</t>
+    <t>Frigorificados – CFAT</t>
+  </si>
+  <si>
+    <t>Panificados</t>
+  </si>
+  <si>
+    <t>Material Elétrico e Eletrônico</t>
+  </si>
+  <si>
+    <t>Provedor de Internet</t>
+  </si>
+  <si>
+    <t>Moto Aquática</t>
+  </si>
+  <si>
+    <t>Gêneros Secos</t>
+  </si>
+  <si>
+    <t>Material de Pintura</t>
+  </si>
+  <si>
+    <t>Gás Liquefeito de Petróleo (GLP)</t>
+  </si>
+  <si>
+    <t>Transporte de Carga</t>
+  </si>
+  <si>
+    <t>Água Mineral</t>
+  </si>
+  <si>
+    <t>Material Permanente de Rancho</t>
+  </si>
+  <si>
+    <t>Material de Carpintaria</t>
+  </si>
+  <si>
+    <t>Bebidas não-alcoólicas</t>
+  </si>
+  <si>
+    <t>Serviços de Ornamentação</t>
+  </si>
+  <si>
+    <t>Montagem de Palanque</t>
+  </si>
+  <si>
+    <t>Material de Expediente</t>
+  </si>
+  <si>
+    <t>Material de Higiene e Limpeza</t>
+  </si>
+  <si>
+    <t>Material para Copa e Cozinha</t>
+  </si>
+  <si>
+    <t>Pisos e Revestimentos</t>
+  </si>
+  <si>
+    <t>Transporte de Pessoal</t>
+  </si>
+  <si>
+    <t>Material de Segurança Orgânica</t>
+  </si>
+  <si>
+    <t>Material Esportivo (PROFESP)</t>
+  </si>
+  <si>
+    <t>Serviços Gráficos Especializados</t>
+  </si>
+  <si>
+    <t>Mobiliários Corporativos</t>
+  </si>
+  <si>
+    <t>Periféricos de Informática</t>
+  </si>
+  <si>
+    <t>Material de Representação</t>
+  </si>
+  <si>
+    <t>Material de Academia</t>
+  </si>
+  <si>
+    <t>Seguro de Viaturas</t>
+  </si>
+  <si>
+    <t>Material Hidráulico</t>
+  </si>
+  <si>
+    <t>Gêneros Frigorificados</t>
+  </si>
+  <si>
+    <t>Gêneros Hortifrutigranjeiros</t>
+  </si>
+  <si>
+    <t>Gêneros Laticínios e Frios</t>
+  </si>
+  <si>
+    <t>Equipamento de Informática</t>
+  </si>
+  <si>
+    <t>Marinharia e Salvatagem</t>
+  </si>
+  <si>
+    <t>Serviços Comuns de Engenharia</t>
+  </si>
+  <si>
+    <t>Agricultura Familiar</t>
+  </si>
+  <si>
+    <t>EBC</t>
+  </si>
+  <si>
+    <t>Gestão de Frota</t>
+  </si>
+  <si>
+    <t>Jardinagem e Paisagismo</t>
+  </si>
+  <si>
+    <t>Transporte de Bagagem</t>
+  </si>
+  <si>
+    <t>Rede de Esgoto do GptFNB</t>
+  </si>
+  <si>
+    <t>Manutenção de Elevadores</t>
+  </si>
+  <si>
+    <t>Concertina, portão e gradil</t>
+  </si>
+  <si>
+    <t>Cestas Básicas</t>
+  </si>
+  <si>
+    <t>Nova Sede da CFB</t>
+  </si>
+  <si>
+    <t>Telefonia Fixa</t>
+  </si>
+  <si>
+    <t>prestação de serviços de Provedor de Internet</t>
+  </si>
+  <si>
+    <t>Água Mineral para atendimento das demandas do CeIMBra e OM apoiadas</t>
+  </si>
+  <si>
+    <t>Material Permanente de Rancho para atendimento das necessi.....</t>
+  </si>
+  <si>
+    <t>Bebidas não-alcoólicas para atendimento das necessidades do CeIMBra e demais organizações militares apoiadas</t>
+  </si>
+  <si>
+    <t>Serviços de ornamentação, montagem de estruturas e adequação de
+espaços internos e externos</t>
+  </si>
+  <si>
+    <t>Serviços de Montagem e desmontagem de palanques em estrutura
+metálica, locação de equipamentos audiovisuais, sonorização e geradores
+elétricos e banheiros químicos</t>
+  </si>
+  <si>
+    <t>Aquisição de material de higiene e limpeza a fim de atender as necessidades dos diversos setores do Comando do 7º Distrito Naval e Órgãos participantes</t>
+  </si>
+  <si>
+    <t>aquisição de Periféricos de Informática</t>
+  </si>
+  <si>
+    <t>Aquisição de material de representação</t>
+  </si>
+  <si>
+    <t>serviço de Telefonia Fixa</t>
+  </si>
+  <si>
+    <t>787310</t>
   </si>
   <si>
     <t>787010</t>
   </si>
   <si>
+    <t>787000</t>
+  </si>
+  <si>
+    <t>787400</t>
+  </si>
+  <si>
+    <t>787320</t>
+  </si>
+  <si>
+    <t>787200</t>
+  </si>
+  <si>
+    <t>787900</t>
+  </si>
+  <si>
+    <t>CAPITANIA FLUVIAL DE ARAGUAIA-TOCANTINS</t>
+  </si>
+  <si>
     <t>CENTRO DE INTENDÊNCIA DA MARINHA EM BRASÍLIA</t>
   </si>
   <si>
+    <t>COMANDO DO 7º DISTRITO NAVAL</t>
+  </si>
+  <si>
+    <t>ESTAÇÃO RÁDIO DA MARINHA EM BRASÍLIA</t>
+  </si>
+  <si>
+    <t>CAPITANIA FLUVIAL DE BRASÍLIA</t>
+  </si>
+  <si>
+    <t>GRUPAMENTO DE FUZILEIROS NAVAIS DE BRASÍLIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE INSTRUÇÃO E ADESTRAMENTO DE BRASÍLIA</t>
+  </si>
+  <si>
+    <t>CFAT</t>
+  </si>
+  <si>
     <t>CeIMBra</t>
   </si>
   <si>
+    <t>Com7ºDN</t>
+  </si>
+  <si>
+    <t>ERMB</t>
+  </si>
+  <si>
+    <t>CFB</t>
+  </si>
+  <si>
+    <t>GptFNB</t>
+  </si>
+  <si>
+    <t>CIAB</t>
+  </si>
+  <si>
+    <t>Divisão de Intendência</t>
+  </si>
+  <si>
+    <t>Divisão de Abastecimento</t>
+  </si>
+  <si>
+    <t>Divisão de Serviços Gerais</t>
+  </si>
+  <si>
+    <t>Divisão de Municiamento</t>
+  </si>
+  <si>
+    <t>Assessoria de Comunicação Social</t>
+  </si>
+  <si>
+    <t>Divisão de Controle Patrimonial</t>
+  </si>
+  <si>
+    <t>SPI</t>
+  </si>
+  <si>
+    <t>DEPARTAMENTO DE TECNOLOGIA DA INFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>ASSESSORIA DE COMUNICAÇÃO SOCIAL</t>
+  </si>
+  <si>
+    <t>DIVISÃO DE SAÚDE E EDUCAÇÃO FÍSICA</t>
+  </si>
+  <si>
+    <t>DIVISÃO DE TRANSPORTES</t>
+  </si>
+  <si>
+    <t>DIVISÃO DE TRANSPORTE</t>
+  </si>
+  <si>
+    <t>Seção de Requisição de Passagens e Bagagens</t>
+  </si>
+  <si>
+    <t>R$ 325.239,20</t>
+  </si>
+  <si>
+    <t>R$ 4.500.025,00</t>
+  </si>
+  <si>
+    <t>R$ 2.138.628,37</t>
+  </si>
+  <si>
+    <t>R$ 151.200,00</t>
+  </si>
+  <si>
+    <t>R$ 1.040.000,00</t>
+  </si>
+  <si>
+    <t>R$ 25.152.088,87</t>
+  </si>
+  <si>
+    <t>R$ 1.532,00</t>
+  </si>
+  <si>
+    <t>R$ 1.128.460,00</t>
+  </si>
+  <si>
+    <t>R$ 0,00</t>
+  </si>
+  <si>
+    <t>R$ 249.999,00</t>
+  </si>
+  <si>
+    <t>R$ 3.822.074,00</t>
+  </si>
+  <si>
+    <t>R$ 1.685.509,00</t>
+  </si>
+  <si>
+    <t>R$ 3.436.038,50</t>
+  </si>
+  <si>
+    <t>R$ 9.508.413,80</t>
+  </si>
+  <si>
+    <t>R$ 3.916.344,84</t>
+  </si>
+  <si>
+    <t>R$ 3.096.464,64</t>
+  </si>
+  <si>
+    <t>R$ 3.577.824,73</t>
+  </si>
+  <si>
+    <t>R$ 4.245.297,80</t>
+  </si>
+  <si>
+    <t>R$ 3.136.514,46</t>
+  </si>
+  <si>
+    <t>R$ 120.768,00</t>
+  </si>
+  <si>
+    <t>R$ 968.774,04</t>
+  </si>
+  <si>
+    <t>R$ 1.154.163,00</t>
+  </si>
+  <si>
+    <t>R$ 6.747.823,40</t>
+  </si>
+  <si>
+    <t>R$ 1.614.627,00</t>
+  </si>
+  <si>
+    <t>R$ 374.823,00</t>
+  </si>
+  <si>
+    <t>R$ 234.234,00</t>
+  </si>
+  <si>
     <t>Não</t>
+  </si>
+  <si>
+    <t>Sim</t>
   </si>
 </sst>
 </file>
@@ -509,10 +1229,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,126 +1281,2272 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J2" t="s">
+        <v>223</v>
+      </c>
+      <c r="K2" t="s">
+        <v>230</v>
+      </c>
+      <c r="L2" t="s">
+        <v>237</v>
+      </c>
+      <c r="M2" t="s">
+        <v>237</v>
+      </c>
+      <c r="N2" t="s">
+        <v>257</v>
+      </c>
+      <c r="O2" t="s">
+        <v>283</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K3" t="s">
+        <v>231</v>
+      </c>
+      <c r="L3" t="s">
+        <v>238</v>
+      </c>
+      <c r="N3" t="s">
+        <v>258</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" t="s">
+        <v>169</v>
+      </c>
+      <c r="J4" t="s">
+        <v>225</v>
+      </c>
+      <c r="K4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L4" t="s">
+        <v>239</v>
+      </c>
+      <c r="N4" t="s">
+        <v>259</v>
+      </c>
+      <c r="O4" t="s">
+        <v>284</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" t="s">
+        <v>165</v>
+      </c>
+      <c r="H5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J5" t="s">
+        <v>226</v>
+      </c>
+      <c r="K5" t="s">
+        <v>233</v>
+      </c>
+      <c r="L5" t="s">
+        <v>240</v>
+      </c>
+      <c r="M5" t="s">
+        <v>244</v>
+      </c>
+      <c r="N5" t="s">
+        <v>260</v>
+      </c>
+      <c r="O5" t="s">
+        <v>283</v>
+      </c>
+      <c r="P5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H6" t="s">
+        <v>171</v>
+      </c>
+      <c r="J6" t="s">
+        <v>227</v>
+      </c>
+      <c r="K6" t="s">
+        <v>234</v>
+      </c>
+      <c r="L6" t="s">
+        <v>241</v>
+      </c>
+      <c r="N6" t="s">
+        <v>261</v>
+      </c>
+      <c r="O6" t="s">
+        <v>283</v>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H7" t="s">
+        <v>172</v>
+      </c>
+      <c r="J7" t="s">
+        <v>224</v>
+      </c>
+      <c r="K7" t="s">
+        <v>231</v>
+      </c>
+      <c r="L7" t="s">
+        <v>238</v>
+      </c>
+      <c r="N7" t="s">
+        <v>262</v>
+      </c>
+      <c r="O7" t="s">
+        <v>283</v>
+      </c>
+      <c r="P7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" t="s">
+        <v>225</v>
+      </c>
+      <c r="K8" t="s">
+        <v>232</v>
+      </c>
+      <c r="L8" t="s">
+        <v>239</v>
+      </c>
+      <c r="N8" t="s">
+        <v>263</v>
+      </c>
+      <c r="O8" t="s">
+        <v>283</v>
+      </c>
+      <c r="P8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J9" t="s">
+        <v>228</v>
+      </c>
+      <c r="K9" t="s">
+        <v>235</v>
+      </c>
+      <c r="L9" t="s">
+        <v>242</v>
+      </c>
+      <c r="N9" t="s">
+        <v>264</v>
+      </c>
+      <c r="O9" t="s">
+        <v>283</v>
+      </c>
+      <c r="P9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" t="s">
+        <v>175</v>
+      </c>
+      <c r="J10" t="s">
+        <v>224</v>
+      </c>
+      <c r="K10" t="s">
+        <v>231</v>
+      </c>
+      <c r="L10" t="s">
+        <v>238</v>
+      </c>
+      <c r="M10" t="s">
+        <v>245</v>
+      </c>
+      <c r="N10" t="s">
+        <v>265</v>
+      </c>
+      <c r="O10" t="s">
+        <v>283</v>
+      </c>
+      <c r="P10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" t="s">
+        <v>164</v>
+      </c>
+      <c r="H11" t="s">
+        <v>176</v>
+      </c>
+      <c r="I11" t="s">
+        <v>214</v>
+      </c>
+      <c r="J11" t="s">
+        <v>224</v>
+      </c>
+      <c r="K11" t="s">
+        <v>231</v>
+      </c>
+      <c r="L11" t="s">
+        <v>238</v>
+      </c>
+      <c r="N11" t="s">
+        <v>266</v>
+      </c>
+      <c r="O11" t="s">
+        <v>283</v>
+      </c>
+      <c r="P11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" t="s">
+        <v>164</v>
+      </c>
+      <c r="H12" t="s">
+        <v>177</v>
+      </c>
+      <c r="I12" t="s">
+        <v>215</v>
+      </c>
+      <c r="J12" t="s">
+        <v>228</v>
+      </c>
+      <c r="K12" t="s">
+        <v>235</v>
+      </c>
+      <c r="L12" t="s">
+        <v>242</v>
+      </c>
+      <c r="N12" t="s">
+        <v>267</v>
+      </c>
+      <c r="O12" t="s">
+        <v>283</v>
+      </c>
+      <c r="P12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" t="s">
+        <v>164</v>
+      </c>
+      <c r="H13" t="s">
+        <v>178</v>
+      </c>
+      <c r="J13" t="s">
+        <v>225</v>
+      </c>
+      <c r="K13" t="s">
+        <v>232</v>
+      </c>
+      <c r="L13" t="s">
+        <v>239</v>
+      </c>
+      <c r="M13" t="s">
+        <v>246</v>
+      </c>
+      <c r="N13" t="s">
+        <v>265</v>
+      </c>
+      <c r="O13" t="s">
+        <v>284</v>
+      </c>
+      <c r="P13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" t="s">
+        <v>116</v>
+      </c>
+      <c r="F14" t="s">
+        <v>127</v>
+      </c>
+      <c r="G14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H14" t="s">
+        <v>179</v>
+      </c>
+      <c r="I14" t="s">
+        <v>216</v>
+      </c>
+      <c r="J14" t="s">
+        <v>224</v>
+      </c>
+      <c r="K14" t="s">
+        <v>231</v>
+      </c>
+      <c r="L14" t="s">
+        <v>238</v>
+      </c>
+      <c r="M14" t="s">
+        <v>247</v>
+      </c>
+      <c r="N14" t="s">
+        <v>268</v>
+      </c>
+      <c r="O14" t="s">
+        <v>284</v>
+      </c>
+      <c r="P14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" t="s">
+        <v>165</v>
+      </c>
+      <c r="H15" t="s">
+        <v>180</v>
+      </c>
+      <c r="I15" t="s">
+        <v>217</v>
+      </c>
+      <c r="J15" t="s">
+        <v>225</v>
+      </c>
+      <c r="K15" t="s">
+        <v>232</v>
+      </c>
+      <c r="L15" t="s">
+        <v>239</v>
+      </c>
+      <c r="M15" t="s">
+        <v>248</v>
+      </c>
+      <c r="N15" t="s">
+        <v>269</v>
+      </c>
+      <c r="O15" t="s">
+        <v>284</v>
+      </c>
+      <c r="P15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" t="s">
+        <v>129</v>
+      </c>
+      <c r="G16" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" t="s">
+        <v>181</v>
+      </c>
+      <c r="I16" t="s">
+        <v>218</v>
+      </c>
+      <c r="J16" t="s">
+        <v>225</v>
+      </c>
+      <c r="K16" t="s">
+        <v>232</v>
+      </c>
+      <c r="L16" t="s">
+        <v>239</v>
+      </c>
+      <c r="M16" t="s">
+        <v>248</v>
+      </c>
+      <c r="N16" t="s">
+        <v>270</v>
+      </c>
+      <c r="O16" t="s">
+        <v>284</v>
+      </c>
+      <c r="P16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G17" t="s">
+        <v>164</v>
+      </c>
+      <c r="H17" t="s">
+        <v>182</v>
+      </c>
+      <c r="J17" t="s">
+        <v>225</v>
+      </c>
+      <c r="K17" t="s">
+        <v>232</v>
+      </c>
+      <c r="L17" t="s">
+        <v>239</v>
+      </c>
+      <c r="M17" t="s">
+        <v>249</v>
+      </c>
+      <c r="N17" t="s">
+        <v>271</v>
+      </c>
+      <c r="O17" t="s">
+        <v>284</v>
+      </c>
+      <c r="P17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" t="s">
+        <v>164</v>
+      </c>
+      <c r="H18" t="s">
+        <v>183</v>
+      </c>
+      <c r="I18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J18" t="s">
+        <v>225</v>
+      </c>
+      <c r="K18" t="s">
+        <v>232</v>
+      </c>
+      <c r="L18" t="s">
+        <v>239</v>
+      </c>
+      <c r="M18" t="s">
+        <v>249</v>
+      </c>
+      <c r="N18" t="s">
+        <v>272</v>
+      </c>
+      <c r="O18" t="s">
+        <v>283</v>
+      </c>
+      <c r="P18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" t="s">
+        <v>164</v>
+      </c>
+      <c r="H19" t="s">
+        <v>184</v>
+      </c>
+      <c r="J19" t="s">
+        <v>224</v>
+      </c>
+      <c r="K19" t="s">
+        <v>231</v>
+      </c>
+      <c r="L19" t="s">
+        <v>238</v>
+      </c>
+      <c r="M19" t="s">
+        <v>247</v>
+      </c>
+      <c r="N19" t="s">
+        <v>265</v>
+      </c>
+      <c r="O19" t="s">
+        <v>284</v>
+      </c>
+      <c r="P19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G20" t="s">
+        <v>164</v>
+      </c>
+      <c r="H20" t="s">
+        <v>185</v>
+      </c>
+      <c r="J20" t="s">
+        <v>225</v>
+      </c>
+      <c r="K20" t="s">
+        <v>232</v>
+      </c>
+      <c r="L20" t="s">
+        <v>239</v>
+      </c>
+      <c r="M20" t="s">
+        <v>250</v>
+      </c>
+      <c r="N20" t="s">
+        <v>265</v>
+      </c>
+      <c r="O20" t="s">
+        <v>284</v>
+      </c>
+      <c r="P20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" t="s">
+        <v>134</v>
+      </c>
+      <c r="G21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H21" t="s">
+        <v>186</v>
+      </c>
+      <c r="J21" t="s">
+        <v>225</v>
+      </c>
+      <c r="K21" t="s">
+        <v>232</v>
+      </c>
+      <c r="L21" t="s">
+        <v>239</v>
+      </c>
+      <c r="N21" t="s">
+        <v>265</v>
+      </c>
+      <c r="P21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" t="s">
+        <v>164</v>
+      </c>
+      <c r="H22" t="s">
+        <v>187</v>
+      </c>
+      <c r="J22" t="s">
+        <v>225</v>
+      </c>
+      <c r="K22" t="s">
+        <v>232</v>
+      </c>
+      <c r="L22" t="s">
+        <v>239</v>
+      </c>
+      <c r="N22" t="s">
+        <v>265</v>
+      </c>
+      <c r="O22" t="s">
+        <v>283</v>
+      </c>
+      <c r="P22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G23" t="s">
+        <v>164</v>
+      </c>
+      <c r="H23" t="s">
+        <v>188</v>
+      </c>
+      <c r="J23" t="s">
+        <v>226</v>
+      </c>
+      <c r="K23" t="s">
+        <v>233</v>
+      </c>
+      <c r="L23" t="s">
+        <v>240</v>
+      </c>
+      <c r="N23" t="s">
+        <v>265</v>
+      </c>
+      <c r="O23" t="s">
+        <v>284</v>
+      </c>
+      <c r="P23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" t="s">
+        <v>165</v>
+      </c>
+      <c r="H24" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" t="s">
+        <v>229</v>
+      </c>
+      <c r="K24" t="s">
+        <v>236</v>
+      </c>
+      <c r="L24" t="s">
+        <v>243</v>
+      </c>
+      <c r="N24" t="s">
+        <v>265</v>
+      </c>
+      <c r="O24" t="s">
+        <v>283</v>
+      </c>
+      <c r="P24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" t="s">
+        <v>138</v>
+      </c>
+      <c r="G25" t="s">
+        <v>164</v>
+      </c>
+      <c r="H25" t="s">
+        <v>190</v>
+      </c>
+      <c r="J25" t="s">
+        <v>227</v>
+      </c>
+      <c r="K25" t="s">
+        <v>234</v>
+      </c>
+      <c r="L25" t="s">
+        <v>241</v>
+      </c>
+      <c r="M25" t="s">
+        <v>241</v>
+      </c>
+      <c r="N25" t="s">
+        <v>265</v>
+      </c>
+      <c r="O25" t="s">
+        <v>284</v>
+      </c>
+      <c r="P25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" t="s">
+        <v>139</v>
+      </c>
+      <c r="G26" t="s">
+        <v>164</v>
+      </c>
+      <c r="H26" t="s">
+        <v>191</v>
+      </c>
+      <c r="I26" t="s">
+        <v>220</v>
+      </c>
+      <c r="J26" t="s">
+        <v>225</v>
+      </c>
+      <c r="K26" t="s">
+        <v>232</v>
+      </c>
+      <c r="L26" t="s">
+        <v>239</v>
+      </c>
+      <c r="M26" t="s">
+        <v>251</v>
+      </c>
+      <c r="N26" t="s">
+        <v>265</v>
+      </c>
+      <c r="O26" t="s">
+        <v>284</v>
+      </c>
+      <c r="P26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" t="s">
+        <v>140</v>
+      </c>
+      <c r="G27" t="s">
+        <v>164</v>
+      </c>
+      <c r="H27" t="s">
+        <v>192</v>
+      </c>
+      <c r="I27" t="s">
+        <v>221</v>
+      </c>
+      <c r="J27" t="s">
+        <v>225</v>
+      </c>
+      <c r="K27" t="s">
+        <v>232</v>
+      </c>
+      <c r="L27" t="s">
+        <v>239</v>
+      </c>
+      <c r="M27" t="s">
+        <v>252</v>
+      </c>
+      <c r="N27" t="s">
+        <v>265</v>
+      </c>
+      <c r="O27" t="s">
+        <v>284</v>
+      </c>
+      <c r="P27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" t="s">
+        <v>141</v>
+      </c>
+      <c r="G28" t="s">
+        <v>164</v>
+      </c>
+      <c r="H28" t="s">
+        <v>193</v>
+      </c>
+      <c r="J28" t="s">
+        <v>225</v>
+      </c>
+      <c r="K28" t="s">
+        <v>232</v>
+      </c>
+      <c r="L28" t="s">
+        <v>239</v>
+      </c>
+      <c r="M28" t="s">
+        <v>253</v>
+      </c>
+      <c r="N28" t="s">
+        <v>265</v>
+      </c>
+      <c r="O28" t="s">
+        <v>284</v>
+      </c>
+      <c r="P28">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J29" t="s">
+        <v>225</v>
+      </c>
+      <c r="K29" t="s">
+        <v>232</v>
+      </c>
+      <c r="L29" t="s">
+        <v>239</v>
+      </c>
+      <c r="M29" t="s">
+        <v>254</v>
+      </c>
+      <c r="N29" t="s">
+        <v>265</v>
+      </c>
+      <c r="O29" t="s">
+        <v>283</v>
+      </c>
+      <c r="P29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" t="s">
+        <v>143</v>
+      </c>
+      <c r="G30" t="s">
+        <v>164</v>
+      </c>
+      <c r="H30" t="s">
+        <v>195</v>
+      </c>
+      <c r="J30" t="s">
+        <v>225</v>
+      </c>
+      <c r="K30" t="s">
+        <v>232</v>
+      </c>
+      <c r="L30" t="s">
+        <v>239</v>
+      </c>
+      <c r="M30" t="s">
+        <v>246</v>
+      </c>
+      <c r="N30" t="s">
+        <v>265</v>
+      </c>
+      <c r="O30" t="s">
+        <v>283</v>
+      </c>
+      <c r="P30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" t="s">
+        <v>164</v>
+      </c>
+      <c r="H31" t="s">
+        <v>196</v>
+      </c>
+      <c r="J31" t="s">
+        <v>224</v>
+      </c>
+      <c r="K31" t="s">
+        <v>231</v>
+      </c>
+      <c r="L31" t="s">
+        <v>238</v>
+      </c>
+      <c r="M31" t="s">
+        <v>247</v>
+      </c>
+      <c r="N31" t="s">
+        <v>265</v>
+      </c>
+      <c r="O31" t="s">
+        <v>284</v>
+      </c>
+      <c r="P31">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" t="s">
+        <v>164</v>
+      </c>
+      <c r="H32" t="s">
+        <v>197</v>
+      </c>
+      <c r="J32" t="s">
+        <v>224</v>
+      </c>
+      <c r="K32" t="s">
+        <v>231</v>
+      </c>
+      <c r="L32" t="s">
+        <v>238</v>
+      </c>
+      <c r="M32" t="s">
+        <v>247</v>
+      </c>
+      <c r="N32" t="s">
+        <v>273</v>
+      </c>
+      <c r="O32" t="s">
+        <v>284</v>
+      </c>
+      <c r="P32">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" t="s">
+        <v>146</v>
+      </c>
+      <c r="G33" t="s">
+        <v>164</v>
+      </c>
+      <c r="H33" t="s">
+        <v>172</v>
+      </c>
+      <c r="J33" t="s">
+        <v>224</v>
+      </c>
+      <c r="K33" t="s">
+        <v>231</v>
+      </c>
+      <c r="L33" t="s">
+        <v>238</v>
+      </c>
+      <c r="M33" t="s">
+        <v>247</v>
+      </c>
+      <c r="N33" t="s">
+        <v>265</v>
+      </c>
+      <c r="O33" t="s">
+        <v>284</v>
+      </c>
+      <c r="P33">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s">
+        <v>147</v>
+      </c>
+      <c r="G34" t="s">
+        <v>164</v>
+      </c>
+      <c r="H34" t="s">
+        <v>198</v>
+      </c>
+      <c r="J34" t="s">
+        <v>224</v>
+      </c>
+      <c r="K34" t="s">
+        <v>231</v>
+      </c>
+      <c r="L34" t="s">
+        <v>238</v>
+      </c>
+      <c r="M34" t="s">
+        <v>247</v>
+      </c>
+      <c r="N34" t="s">
+        <v>274</v>
+      </c>
+      <c r="O34" t="s">
+        <v>284</v>
+      </c>
+      <c r="P34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35" t="s">
+        <v>148</v>
+      </c>
+      <c r="G35" t="s">
+        <v>164</v>
+      </c>
+      <c r="H35" t="s">
+        <v>199</v>
+      </c>
+      <c r="J35" t="s">
+        <v>225</v>
+      </c>
+      <c r="K35" t="s">
+        <v>232</v>
+      </c>
+      <c r="L35" t="s">
+        <v>239</v>
+      </c>
+      <c r="M35" t="s">
+        <v>251</v>
+      </c>
+      <c r="N35" t="s">
+        <v>265</v>
+      </c>
+      <c r="O35" t="s">
+        <v>284</v>
+      </c>
+      <c r="P35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" t="s">
+        <v>164</v>
+      </c>
+      <c r="H36" t="s">
+        <v>200</v>
+      </c>
+      <c r="J36" t="s">
+        <v>227</v>
+      </c>
+      <c r="K36" t="s">
+        <v>234</v>
+      </c>
+      <c r="L36" t="s">
+        <v>241</v>
+      </c>
+      <c r="M36" t="s">
+        <v>241</v>
+      </c>
+      <c r="N36" t="s">
+        <v>265</v>
+      </c>
+      <c r="O36" t="s">
+        <v>284</v>
+      </c>
+      <c r="P36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37" t="s">
+        <v>150</v>
+      </c>
+      <c r="G37" t="s">
+        <v>164</v>
+      </c>
+      <c r="H37" t="s">
+        <v>201</v>
+      </c>
+      <c r="J37" t="s">
+        <v>223</v>
+      </c>
+      <c r="K37" t="s">
+        <v>230</v>
+      </c>
+      <c r="L37" t="s">
+        <v>237</v>
+      </c>
+      <c r="N37" t="s">
+        <v>265</v>
+      </c>
+      <c r="O37" t="s">
+        <v>283</v>
+      </c>
+      <c r="P37">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" t="s">
+        <v>116</v>
+      </c>
+      <c r="F38" t="s">
+        <v>151</v>
+      </c>
+      <c r="G38" t="s">
+        <v>164</v>
+      </c>
+      <c r="H38" t="s">
+        <v>202</v>
+      </c>
+      <c r="J38" t="s">
+        <v>224</v>
+      </c>
+      <c r="K38" t="s">
+        <v>231</v>
+      </c>
+      <c r="L38" t="s">
+        <v>238</v>
+      </c>
+      <c r="N38" t="s">
+        <v>275</v>
+      </c>
+      <c r="O38" t="s">
+        <v>283</v>
+      </c>
+      <c r="P38">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" t="s">
+        <v>116</v>
+      </c>
+      <c r="F39" t="s">
+        <v>152</v>
+      </c>
+      <c r="G39" t="s">
+        <v>164</v>
+      </c>
+      <c r="H39" t="s">
+        <v>203</v>
+      </c>
+      <c r="J39" t="s">
+        <v>224</v>
+      </c>
+      <c r="K39" t="s">
+        <v>231</v>
+      </c>
+      <c r="L39" t="s">
+        <v>238</v>
+      </c>
+      <c r="N39" t="s">
+        <v>276</v>
+      </c>
+      <c r="O39" t="s">
+        <v>283</v>
+      </c>
+      <c r="P39">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>105</v>
+      </c>
+      <c r="E40" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" t="s">
+        <v>153</v>
+      </c>
+      <c r="G40" t="s">
+        <v>165</v>
+      </c>
+      <c r="H40" t="s">
+        <v>204</v>
+      </c>
+      <c r="J40" t="s">
+        <v>225</v>
+      </c>
+      <c r="K40" t="s">
+        <v>232</v>
+      </c>
+      <c r="L40" t="s">
+        <v>239</v>
+      </c>
+      <c r="M40" t="s">
+        <v>255</v>
+      </c>
+      <c r="N40" t="s">
+        <v>265</v>
+      </c>
+      <c r="O40" t="s">
+        <v>283</v>
+      </c>
+      <c r="P40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" t="s">
+        <v>154</v>
+      </c>
+      <c r="G41" t="s">
+        <v>166</v>
+      </c>
+      <c r="H41" t="s">
+        <v>205</v>
+      </c>
+      <c r="J41" t="s">
+        <v>225</v>
+      </c>
+      <c r="K41" t="s">
+        <v>232</v>
+      </c>
+      <c r="L41" t="s">
+        <v>239</v>
+      </c>
+      <c r="N41" t="s">
+        <v>265</v>
+      </c>
+      <c r="O41" t="s">
+        <v>283</v>
+      </c>
+      <c r="P41">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>107</v>
+      </c>
+      <c r="E42" t="s">
+        <v>116</v>
+      </c>
+      <c r="F42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G42" t="s">
+        <v>165</v>
+      </c>
+      <c r="H42" t="s">
+        <v>206</v>
+      </c>
+      <c r="I42" t="s">
+        <v>206</v>
+      </c>
+      <c r="J42" t="s">
+        <v>224</v>
+      </c>
+      <c r="K42" t="s">
+        <v>231</v>
+      </c>
+      <c r="L42" t="s">
+        <v>238</v>
+      </c>
+      <c r="M42" t="s">
+        <v>256</v>
+      </c>
+      <c r="N42" t="s">
+        <v>265</v>
+      </c>
+      <c r="O42" t="s">
+        <v>283</v>
+      </c>
+      <c r="P42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>108</v>
+      </c>
+      <c r="E43" t="s">
+        <v>116</v>
+      </c>
+      <c r="F43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G43" t="s">
+        <v>165</v>
+      </c>
+      <c r="H43" t="s">
+        <v>207</v>
+      </c>
+      <c r="I43" t="s">
+        <v>207</v>
+      </c>
+      <c r="J43" t="s">
+        <v>228</v>
+      </c>
+      <c r="K43" t="s">
+        <v>235</v>
+      </c>
+      <c r="L43" t="s">
+        <v>242</v>
+      </c>
+      <c r="N43" t="s">
+        <v>265</v>
+      </c>
+      <c r="O43" t="s">
+        <v>283</v>
+      </c>
+      <c r="P43">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>109</v>
+      </c>
+      <c r="E44" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" t="s">
+        <v>157</v>
+      </c>
+      <c r="G44" t="s">
+        <v>165</v>
+      </c>
+      <c r="H44" t="s">
+        <v>208</v>
+      </c>
+      <c r="J44" t="s">
+        <v>225</v>
+      </c>
+      <c r="K44" t="s">
+        <v>232</v>
+      </c>
+      <c r="L44" t="s">
+        <v>239</v>
+      </c>
+      <c r="N44" t="s">
+        <v>277</v>
+      </c>
+      <c r="O44" t="s">
+        <v>283</v>
+      </c>
+      <c r="P44">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" t="s">
+        <v>116</v>
+      </c>
+      <c r="F45" t="s">
+        <v>158</v>
+      </c>
+      <c r="G45" t="s">
+        <v>164</v>
+      </c>
+      <c r="H45" t="s">
+        <v>209</v>
+      </c>
+      <c r="J45" t="s">
+        <v>226</v>
+      </c>
+      <c r="K45" t="s">
+        <v>233</v>
+      </c>
+      <c r="L45" t="s">
+        <v>240</v>
+      </c>
+      <c r="M45" t="s">
+        <v>240</v>
+      </c>
+      <c r="N45" t="s">
+        <v>265</v>
+      </c>
+      <c r="O45" t="s">
+        <v>284</v>
+      </c>
+      <c r="P45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" t="s">
+        <v>116</v>
+      </c>
+      <c r="F46" t="s">
+        <v>159</v>
+      </c>
+      <c r="G46" t="s">
+        <v>164</v>
+      </c>
+      <c r="H46" t="s">
+        <v>210</v>
+      </c>
+      <c r="J46" t="s">
+        <v>225</v>
+      </c>
+      <c r="K46" t="s">
+        <v>232</v>
+      </c>
+      <c r="L46" t="s">
+        <v>239</v>
+      </c>
+      <c r="N46" t="s">
+        <v>278</v>
+      </c>
+      <c r="O46" t="s">
+        <v>283</v>
+      </c>
+      <c r="P46">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R3" t="s">
-        <v>45</v>
+      <c r="B47" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>76</v>
+      </c>
+      <c r="E47" t="s">
+        <v>116</v>
+      </c>
+      <c r="F47" t="s">
+        <v>160</v>
+      </c>
+      <c r="G47" t="s">
+        <v>165</v>
+      </c>
+      <c r="H47" t="s">
+        <v>211</v>
+      </c>
+      <c r="J47" t="s">
+        <v>227</v>
+      </c>
+      <c r="K47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L47" t="s">
+        <v>241</v>
+      </c>
+      <c r="N47" t="s">
+        <v>279</v>
+      </c>
+      <c r="O47" t="s">
+        <v>283</v>
+      </c>
+      <c r="P47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" t="s">
+        <v>116</v>
+      </c>
+      <c r="F48" t="s">
+        <v>161</v>
+      </c>
+      <c r="G48" t="s">
+        <v>165</v>
+      </c>
+      <c r="H48" t="s">
+        <v>208</v>
+      </c>
+      <c r="J48" t="s">
+        <v>225</v>
+      </c>
+      <c r="K48" t="s">
+        <v>232</v>
+      </c>
+      <c r="L48" t="s">
+        <v>239</v>
+      </c>
+      <c r="M48" t="s">
+        <v>246</v>
+      </c>
+      <c r="N48" t="s">
+        <v>280</v>
+      </c>
+      <c r="O48" t="s">
+        <v>283</v>
+      </c>
+      <c r="P48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" t="s">
+        <v>113</v>
+      </c>
+      <c r="E49" t="s">
+        <v>116</v>
+      </c>
+      <c r="F49" t="s">
+        <v>162</v>
+      </c>
+      <c r="G49" t="s">
+        <v>164</v>
+      </c>
+      <c r="H49" t="s">
+        <v>210</v>
+      </c>
+      <c r="J49" t="s">
+        <v>225</v>
+      </c>
+      <c r="K49" t="s">
+        <v>232</v>
+      </c>
+      <c r="L49" t="s">
+        <v>239</v>
+      </c>
+      <c r="N49" t="s">
+        <v>281</v>
+      </c>
+      <c r="O49" t="s">
+        <v>284</v>
+      </c>
+      <c r="P49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" t="s">
+        <v>116</v>
+      </c>
+      <c r="F50" t="s">
+        <v>163</v>
+      </c>
+      <c r="G50" t="s">
+        <v>164</v>
+      </c>
+      <c r="H50" t="s">
+        <v>212</v>
+      </c>
+      <c r="I50" t="s">
+        <v>222</v>
+      </c>
+      <c r="J50" t="s">
+        <v>225</v>
+      </c>
+      <c r="K50" t="s">
+        <v>232</v>
+      </c>
+      <c r="L50" t="s">
+        <v>239</v>
+      </c>
+      <c r="N50" t="s">
+        <v>282</v>
+      </c>
+      <c r="O50" t="s">
+        <v>283</v>
+      </c>
+      <c r="P50">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/tabela_completa.xlsx
+++ b/tabela_completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="295">
   <si>
     <t>situacao</t>
   </si>
@@ -64,7 +64,25 @@
     <t>order</t>
   </si>
   <si>
-    <t>Sessão Pública</t>
+    <t>Pré-Publicação</t>
+  </si>
+  <si>
+    <t>Recomendações AGU</t>
+  </si>
+  <si>
+    <t>AGU</t>
+  </si>
+  <si>
+    <t>Nota Técnica</t>
+  </si>
+  <si>
+    <t>Atendimento da NT</t>
+  </si>
+  <si>
+    <t>Montagem do Processo</t>
+  </si>
+  <si>
+    <t>Consolidação de Demanda</t>
   </si>
   <si>
     <t>Planejamento</t>
@@ -73,441 +91,453 @@
     <t>Concluído</t>
   </si>
   <si>
+    <t>Arquivado</t>
+  </si>
+  <si>
+    <t>PE 90031/2024</t>
+  </si>
+  <si>
+    <t>PE 90044/2024</t>
+  </si>
+  <si>
+    <t>TJIL 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90002/2024</t>
+  </si>
+  <si>
+    <t>PE 90019/2024</t>
+  </si>
+  <si>
+    <t>PE 90023/2024</t>
+  </si>
+  <si>
+    <t>PE 90025/2024</t>
+  </si>
+  <si>
+    <t>PE 90026/2024</t>
+  </si>
+  <si>
+    <t>PE 90027/2024</t>
+  </si>
+  <si>
+    <t>PE 90028/2024</t>
+  </si>
+  <si>
+    <t>PE 90036/2024</t>
+  </si>
+  <si>
+    <t>PE 90037/2024</t>
+  </si>
+  <si>
+    <t>PE 08/2023</t>
+  </si>
+  <si>
+    <t>PE 90004/2024</t>
+  </si>
+  <si>
+    <t>PE 90014/2024</t>
+  </si>
+  <si>
+    <t>PE 10/2023</t>
+  </si>
+  <si>
+    <t>PE 90006/2024</t>
+  </si>
+  <si>
+    <t>PE 90007/2024</t>
+  </si>
+  <si>
+    <t>PE 90013/2024</t>
+  </si>
+  <si>
+    <t>PE 90015/2024</t>
+  </si>
+  <si>
+    <t>PE 90016/2024</t>
+  </si>
+  <si>
+    <t>PE 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90011/2024</t>
+  </si>
+  <si>
+    <t>PE 90012/2024</t>
+  </si>
+  <si>
+    <t>PE 90017/2024</t>
+  </si>
+  <si>
+    <t>PE 90020/2024</t>
+  </si>
+  <si>
+    <t>PE 90033/2024</t>
+  </si>
+  <si>
     <t>PE 07/2023</t>
   </si>
   <si>
-    <t>PE 08/2023</t>
-  </si>
-  <si>
-    <t>PE 10/2023</t>
+    <t>PE 13/2023</t>
   </si>
   <si>
     <t>PE 90005/2024</t>
   </si>
   <si>
+    <t>PE 90008/2024</t>
+  </si>
+  <si>
     <t>PE 90009/2024</t>
   </si>
   <si>
+    <t>PE 90010/2024</t>
+  </si>
+  <si>
+    <t>PE 90021/2024</t>
+  </si>
+  <si>
+    <t>PE 90022/2024</t>
+  </si>
+  <si>
+    <t>CC 90001/2024</t>
+  </si>
+  <si>
     <t>PE 04/2023</t>
   </si>
   <si>
-    <t>PE 13/2023</t>
-  </si>
-  <si>
-    <t>PE 90001/2024</t>
-  </si>
-  <si>
-    <t>PE 90002/2024</t>
-  </si>
-  <si>
-    <t>PE 90007/2024</t>
-  </si>
-  <si>
-    <t>PE 90008/2024</t>
-  </si>
-  <si>
-    <t>PE 90010/2024</t>
-  </si>
-  <si>
-    <t>PE 90011/2024</t>
-  </si>
-  <si>
-    <t>PE 90012/2024</t>
-  </si>
-  <si>
-    <t>PE 90013/2024</t>
-  </si>
-  <si>
-    <t>PE 90014/2024</t>
-  </si>
-  <si>
-    <t>PE 90015/2024</t>
-  </si>
-  <si>
-    <t>PE 90016/2024</t>
-  </si>
-  <si>
-    <t>PE 90017/2024</t>
+    <t>PE 90003/2024</t>
+  </si>
+  <si>
+    <t>PE 90024/2024</t>
+  </si>
+  <si>
+    <t>PE 90029/2024</t>
+  </si>
+  <si>
+    <t>PE 90032/2024</t>
+  </si>
+  <si>
+    <t>PE 90041/2024</t>
+  </si>
+  <si>
+    <t>PE 90030/2024</t>
+  </si>
+  <si>
+    <t>TJDL 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90038/2024</t>
+  </si>
+  <si>
+    <t>PE 90039/2024</t>
+  </si>
+  <si>
+    <t>PE 90040/2024</t>
+  </si>
+  <si>
+    <t>PE 90035/2024</t>
   </si>
   <si>
     <t>PE 90018/2024</t>
   </si>
   <si>
-    <t>PE 90019/2024</t>
-  </si>
-  <si>
-    <t>PE 90020/2024</t>
-  </si>
-  <si>
-    <t>PE 90021/2024</t>
-  </si>
-  <si>
-    <t>PE 90022/2024</t>
-  </si>
-  <si>
-    <t>PE 90023/2024</t>
-  </si>
-  <si>
-    <t>PE 90024/2024</t>
-  </si>
-  <si>
-    <t>PE 90025/2024</t>
-  </si>
-  <si>
-    <t>PE 90026/2024</t>
-  </si>
-  <si>
-    <t>PE 90027/2024</t>
-  </si>
-  <si>
-    <t>PE 90028/2024</t>
-  </si>
-  <si>
-    <t>PE 90029/2024</t>
-  </si>
-  <si>
-    <t>PE 90030/2024</t>
-  </si>
-  <si>
-    <t>PE 90031/2024</t>
-  </si>
-  <si>
-    <t>PE 90032/2024</t>
-  </si>
-  <si>
-    <t>PE 90033/2024</t>
-  </si>
-  <si>
-    <t>PE 90044/2024</t>
-  </si>
-  <si>
-    <t>TJDL 90001/2024</t>
-  </si>
-  <si>
-    <t>TJIL 90001/2024</t>
-  </si>
-  <si>
-    <t>PE 90035/2024</t>
-  </si>
-  <si>
-    <t>PE 90036/2024</t>
-  </si>
-  <si>
-    <t>PE 90037/2024</t>
-  </si>
-  <si>
-    <t>PE 90038/2024</t>
-  </si>
-  <si>
-    <t>PE 90039/2024</t>
-  </si>
-  <si>
-    <t>PE 90040/2024</t>
-  </si>
-  <si>
-    <t>PE 90041/2024</t>
-  </si>
-  <si>
-    <t>CC 90001/2024</t>
-  </si>
-  <si>
-    <t>PE 90003/2024</t>
-  </si>
-  <si>
-    <t>PE 90004/2024</t>
-  </si>
-  <si>
-    <t>PE 90006/2024</t>
-  </si>
-  <si>
-    <t>Tipo Desconhecido</t>
+    <t>Pregão Eletrônico</t>
+  </si>
+  <si>
+    <t>Termo de Justificativa para Inexigibilidade de Licitação</t>
+  </si>
+  <si>
+    <t>Concorrência</t>
+  </si>
+  <si>
+    <t>Termo de Justificativa para Dispensa de Licitação</t>
+  </si>
+  <si>
+    <t>90031</t>
+  </si>
+  <si>
+    <t>90044</t>
+  </si>
+  <si>
+    <t>90001</t>
+  </si>
+  <si>
+    <t>90002</t>
+  </si>
+  <si>
+    <t>90019</t>
+  </si>
+  <si>
+    <t>90023</t>
+  </si>
+  <si>
+    <t>90025</t>
+  </si>
+  <si>
+    <t>90026</t>
+  </si>
+  <si>
+    <t>90027</t>
+  </si>
+  <si>
+    <t>90028</t>
+  </si>
+  <si>
+    <t>90036</t>
+  </si>
+  <si>
+    <t>90037</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>90004</t>
+  </si>
+  <si>
+    <t>90014</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>90006</t>
+  </si>
+  <si>
+    <t>90007</t>
+  </si>
+  <si>
+    <t>90013</t>
+  </si>
+  <si>
+    <t>90015</t>
+  </si>
+  <si>
+    <t>90016</t>
+  </si>
+  <si>
+    <t>90011</t>
+  </si>
+  <si>
+    <t>90012</t>
+  </si>
+  <si>
+    <t>90017</t>
+  </si>
+  <si>
+    <t>90020</t>
+  </si>
+  <si>
+    <t>90033</t>
   </si>
   <si>
     <t>07</t>
   </si>
   <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>13</t>
   </si>
   <si>
     <t>90005</t>
   </si>
   <si>
+    <t>90008</t>
+  </si>
+  <si>
     <t>90009</t>
   </si>
   <si>
+    <t>90010</t>
+  </si>
+  <si>
+    <t>90021</t>
+  </si>
+  <si>
+    <t>90022</t>
+  </si>
+  <si>
     <t>04</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>90001</t>
-  </si>
-  <si>
-    <t>90002</t>
-  </si>
-  <si>
-    <t>90007</t>
-  </si>
-  <si>
-    <t>90008</t>
-  </si>
-  <si>
-    <t>90010</t>
-  </si>
-  <si>
-    <t>90011</t>
-  </si>
-  <si>
-    <t>90012</t>
-  </si>
-  <si>
-    <t>90013</t>
-  </si>
-  <si>
-    <t>90014</t>
-  </si>
-  <si>
-    <t>90015</t>
-  </si>
-  <si>
-    <t>90016</t>
-  </si>
-  <si>
-    <t>90017</t>
+    <t>90003</t>
+  </si>
+  <si>
+    <t>90024</t>
+  </si>
+  <si>
+    <t>90029</t>
+  </si>
+  <si>
+    <t>90032</t>
+  </si>
+  <si>
+    <t>90041</t>
+  </si>
+  <si>
+    <t>90030</t>
+  </si>
+  <si>
+    <t>90038</t>
+  </si>
+  <si>
+    <t>90039</t>
+  </si>
+  <si>
+    <t>90040</t>
+  </si>
+  <si>
+    <t>90035</t>
   </si>
   <si>
     <t>90018</t>
   </si>
   <si>
-    <t>90019</t>
-  </si>
-  <si>
-    <t>90020</t>
-  </si>
-  <si>
-    <t>90021</t>
-  </si>
-  <si>
-    <t>90022</t>
-  </si>
-  <si>
-    <t>90023</t>
-  </si>
-  <si>
-    <t>90024</t>
-  </si>
-  <si>
-    <t>90025</t>
-  </si>
-  <si>
-    <t>90026</t>
-  </si>
-  <si>
-    <t>90027</t>
-  </si>
-  <si>
-    <t>90028</t>
-  </si>
-  <si>
-    <t>90029</t>
-  </si>
-  <si>
-    <t>90030</t>
-  </si>
-  <si>
-    <t>90031</t>
-  </si>
-  <si>
-    <t>90032</t>
-  </si>
-  <si>
-    <t>90033</t>
-  </si>
-  <si>
-    <t>90044</t>
-  </si>
-  <si>
-    <t>90035</t>
-  </si>
-  <si>
-    <t>90036</t>
-  </si>
-  <si>
-    <t>90037</t>
-  </si>
-  <si>
-    <t>90038</t>
-  </si>
-  <si>
-    <t>90039</t>
-  </si>
-  <si>
-    <t>90040</t>
-  </si>
-  <si>
-    <t>90041</t>
-  </si>
-  <si>
-    <t>90003</t>
-  </si>
-  <si>
-    <t>90004</t>
-  </si>
-  <si>
-    <t>90006</t>
+    <t>2024</t>
   </si>
   <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2024</t>
+    <t>63402.000332/2024-67</t>
+  </si>
+  <si>
+    <t>63402.000327/2024-54</t>
+  </si>
+  <si>
+    <t>62055.000130/2024-40</t>
+  </si>
+  <si>
+    <t>63402.000338/2024-34</t>
+  </si>
+  <si>
+    <t>63402.000360/2024-84</t>
+  </si>
+  <si>
+    <t>63402.000355/2024-71</t>
+  </si>
+  <si>
+    <t>63402.000361/2024-69</t>
+  </si>
+  <si>
+    <t>63402.000325/2024-65</t>
+  </si>
+  <si>
+    <t>63402.000324/2024-11</t>
+  </si>
+  <si>
+    <t>63402.000321/2024-87</t>
+  </si>
+  <si>
+    <t>63402.000750/2024-54</t>
+  </si>
+  <si>
+    <t>63402.000766/2024-67</t>
   </si>
   <si>
     <t>62055.002424/2023-25</t>
   </si>
   <si>
+    <t>63402.000334/2024-56</t>
+  </si>
+  <si>
+    <t>63402.000315/2024-20</t>
+  </si>
+  <si>
     <t>62055.002426/2023-14</t>
   </si>
   <si>
+    <t>63402.000328/2024-07</t>
+  </si>
+  <si>
+    <t>63402.000331/2024-12</t>
+  </si>
+  <si>
+    <t>63402.000289/2024-30</t>
+  </si>
+  <si>
+    <t>63402.000316/2024-74</t>
+  </si>
+  <si>
+    <t>63402.000319/2024-16</t>
+  </si>
+  <si>
+    <t>62055.002463/2023-22</t>
+  </si>
+  <si>
+    <t>63402.000326/2024-18</t>
+  </si>
+  <si>
+    <t>63402.000286/2024-04</t>
+  </si>
+  <si>
+    <t>63402.000317/2024-19</t>
+  </si>
+  <si>
+    <t>63402.000359/2024-50</t>
+  </si>
+  <si>
+    <t>63402.000362/2024-73</t>
+  </si>
+  <si>
     <t>63402.000330/2024-78</t>
   </si>
   <si>
+    <t>63402.000318/2024-63</t>
+  </si>
+  <si>
     <t>63402.000313/2024-31</t>
   </si>
   <si>
+    <t>63402.000314/2024-85</t>
+  </si>
+  <si>
+    <t>63402.000358/2024-13</t>
+  </si>
+  <si>
+    <t>63402.000357/2024-61</t>
+  </si>
+  <si>
+    <t>63402.000800/2024-01</t>
+  </si>
+  <si>
     <t>62055.000344/2023-35</t>
   </si>
   <si>
-    <t>62055.002463/2023-22</t>
-  </si>
-  <si>
-    <t>63402.000338/2024-34</t>
-  </si>
-  <si>
-    <t>63402.000331/2024-12</t>
-  </si>
-  <si>
-    <t>63402.000318/2024-63</t>
-  </si>
-  <si>
-    <t>63402.000314/2024-85</t>
-  </si>
-  <si>
-    <t>63402.000326/2024-18</t>
-  </si>
-  <si>
-    <t>63402.000286/2024-04</t>
-  </si>
-  <si>
-    <t>63402.000289/2024-30</t>
-  </si>
-  <si>
-    <t>63402.000315/2024-20</t>
-  </si>
-  <si>
-    <t>63402.000316/2024-74</t>
-  </si>
-  <si>
-    <t>63402.000319/2024-16</t>
-  </si>
-  <si>
-    <t>63402.000317/2024-19</t>
+    <t>63402.000312/2024-96</t>
+  </si>
+  <si>
+    <t>63402.000354/2024-27</t>
+  </si>
+  <si>
+    <t>63402.000333/2024-10</t>
+  </si>
+  <si>
+    <t>63402.000322/2024-21</t>
+  </si>
+  <si>
+    <t>63402.001090/2024-29</t>
+  </si>
+  <si>
+    <t>63402.000320/2024-32</t>
+  </si>
+  <si>
+    <t>63402.000403/2024-21</t>
+  </si>
+  <si>
+    <t>63402.000881/2024-31</t>
+  </si>
+  <si>
+    <t>63402.000907/2024-41</t>
+  </si>
+  <si>
+    <t>63402.000915/2024-98</t>
+  </si>
+  <si>
+    <t>63402.000702/2024-66</t>
   </si>
   <si>
     <t>63402.000352/2024-38</t>
   </si>
   <si>
-    <t>63402.000360/2024-84</t>
-  </si>
-  <si>
-    <t>63402.000359/2024-50</t>
-  </si>
-  <si>
-    <t>63402.000358/2024-13</t>
-  </si>
-  <si>
-    <t>63402.000357/2024-61</t>
-  </si>
-  <si>
-    <t>63402.000355/2024-71</t>
-  </si>
-  <si>
-    <t>63402.000354/2024-27</t>
-  </si>
-  <si>
-    <t>63402.000361/2024-69</t>
-  </si>
-  <si>
-    <t>63402.000325/2024-65</t>
-  </si>
-  <si>
-    <t>63402.000324/2024-11</t>
-  </si>
-  <si>
-    <t>63402.000321/2024-87</t>
-  </si>
-  <si>
-    <t>63402.000333/2024-10</t>
-  </si>
-  <si>
-    <t>63402.000320/2024-32</t>
-  </si>
-  <si>
-    <t>63402.000332/2024-67</t>
-  </si>
-  <si>
-    <t>63402.000322/2024-21</t>
-  </si>
-  <si>
-    <t>63402.000362/2024-73</t>
-  </si>
-  <si>
-    <t>63402.000327/2024-54</t>
-  </si>
-  <si>
-    <t>63402.000403/2024-21</t>
-  </si>
-  <si>
-    <t>62055.000130/2024-40</t>
-  </si>
-  <si>
-    <t>63402.000702/2024-66</t>
-  </si>
-  <si>
-    <t>63402.000750/2024-54</t>
-  </si>
-  <si>
-    <t>63402.000766/2024-67</t>
-  </si>
-  <si>
-    <t>63402.000881/2024-31</t>
-  </si>
-  <si>
-    <t>63402.000907/2024-41</t>
-  </si>
-  <si>
-    <t>63402.000915/2024-98</t>
-  </si>
-  <si>
-    <t>63402.001090/2024-29</t>
-  </si>
-  <si>
-    <t>63402.000800/2024-01</t>
-  </si>
-  <si>
-    <t>63402.000312/2024-96</t>
-  </si>
-  <si>
-    <t>63402.000334/2024-56</t>
-  </si>
-  <si>
-    <t>63402.000328/2024-07</t>
-  </si>
-  <si>
     <t>material</t>
   </si>
   <si>
@@ -517,158 +547,151 @@
     <t>Serviço</t>
   </si>
   <si>
+    <t>Gêneros Laticínios e Frios</t>
+  </si>
+  <si>
+    <t>Serviços Comuns de Engenharia</t>
+  </si>
+  <si>
+    <t>EBC</t>
+  </si>
+  <si>
+    <t>Transporte de Carga</t>
+  </si>
+  <si>
+    <t>Material de Segurança Orgânica</t>
+  </si>
+  <si>
+    <t>Periféricos de Informática</t>
+  </si>
+  <si>
+    <t>Material de Academia</t>
+  </si>
+  <si>
+    <t>Seguro de Viaturas</t>
+  </si>
+  <si>
+    <t>Material Hidráulico</t>
+  </si>
+  <si>
+    <t>Gêneros Frigorificados</t>
+  </si>
+  <si>
+    <t>Jardinagem e Paisagismo</t>
+  </si>
+  <si>
+    <t>Transporte de Bagagem</t>
+  </si>
+  <si>
+    <t>Panificados</t>
+  </si>
+  <si>
+    <t>Cestas Básicas</t>
+  </si>
+  <si>
+    <t>Material de Expediente</t>
+  </si>
+  <si>
+    <t>Material Elétrico e Eletrônico</t>
+  </si>
+  <si>
+    <t>Telefonia Fixa</t>
+  </si>
+  <si>
+    <t>Água Mineral</t>
+  </si>
+  <si>
+    <t>Montagem de Palanque</t>
+  </si>
+  <si>
+    <t>Material de Higiene e Limpeza</t>
+  </si>
+  <si>
+    <t>Material para Copa e Cozinha</t>
+  </si>
+  <si>
+    <t>Gás Liquefeito de Petróleo (GLP)</t>
+  </si>
+  <si>
+    <t>Bebidas não-alcoólicas</t>
+  </si>
+  <si>
+    <t>Serviços de Ornamentação</t>
+  </si>
+  <si>
+    <t>Pisos e Revestimentos</t>
+  </si>
+  <si>
+    <t>Material Esportivo (PROFESP)</t>
+  </si>
+  <si>
+    <t>Marinharia e Salvatagem</t>
+  </si>
+  <si>
     <t>Frigorificados – CFAT</t>
   </si>
   <si>
-    <t>Panificados</t>
-  </si>
-  <si>
-    <t>Material Elétrico e Eletrônico</t>
+    <t>Material de Pintura</t>
   </si>
   <si>
     <t>Provedor de Internet</t>
   </si>
   <si>
+    <t>Material Permanente de Rancho</t>
+  </si>
+  <si>
     <t>Moto Aquática</t>
   </si>
   <si>
+    <t>Material de Carpintaria</t>
+  </si>
+  <si>
+    <t>Serviços Gráficos Especializados</t>
+  </si>
+  <si>
+    <t>Mobiliários Corporativos</t>
+  </si>
+  <si>
+    <t>Nova Sede da CFB</t>
+  </si>
+  <si>
     <t>Gêneros Secos</t>
   </si>
   <si>
-    <t>Material de Pintura</t>
-  </si>
-  <si>
-    <t>Gás Liquefeito de Petróleo (GLP)</t>
-  </si>
-  <si>
-    <t>Transporte de Carga</t>
-  </si>
-  <si>
-    <t>Água Mineral</t>
-  </si>
-  <si>
-    <t>Material Permanente de Rancho</t>
-  </si>
-  <si>
-    <t>Material de Carpintaria</t>
-  </si>
-  <si>
-    <t>Bebidas não-alcoólicas</t>
-  </si>
-  <si>
-    <t>Serviços de Ornamentação</t>
-  </si>
-  <si>
-    <t>Montagem de Palanque</t>
-  </si>
-  <si>
-    <t>Material de Expediente</t>
-  </si>
-  <si>
-    <t>Material de Higiene e Limpeza</t>
-  </si>
-  <si>
-    <t>Material para Copa e Cozinha</t>
-  </si>
-  <si>
-    <t>Pisos e Revestimentos</t>
+    <t>Manutenção de Elevadores</t>
+  </si>
+  <si>
+    <t>Material de Representação</t>
+  </si>
+  <si>
+    <t>Gêneros Hortifrutigranjeiros</t>
+  </si>
+  <si>
+    <t>Equipamento de Informática</t>
+  </si>
+  <si>
+    <t>Agricultura Familiar</t>
+  </si>
+  <si>
+    <t>Rede de Esgoto do GptFNB</t>
+  </si>
+  <si>
+    <t>Concertina, portão e gradil</t>
+  </si>
+  <si>
+    <t>Gestão de Frota</t>
   </si>
   <si>
     <t>Transporte de Pessoal</t>
   </si>
   <si>
-    <t>Material de Segurança Orgânica</t>
-  </si>
-  <si>
-    <t>Material Esportivo (PROFESP)</t>
-  </si>
-  <si>
-    <t>Serviços Gráficos Especializados</t>
-  </si>
-  <si>
-    <t>Mobiliários Corporativos</t>
-  </si>
-  <si>
-    <t>Periféricos de Informática</t>
-  </si>
-  <si>
-    <t>Material de Representação</t>
-  </si>
-  <si>
-    <t>Material de Academia</t>
-  </si>
-  <si>
-    <t>Seguro de Viaturas</t>
-  </si>
-  <si>
-    <t>Material Hidráulico</t>
-  </si>
-  <si>
-    <t>Gêneros Frigorificados</t>
-  </si>
-  <si>
-    <t>Gêneros Hortifrutigranjeiros</t>
-  </si>
-  <si>
-    <t>Gêneros Laticínios e Frios</t>
-  </si>
-  <si>
-    <t>Equipamento de Informática</t>
-  </si>
-  <si>
-    <t>Marinharia e Salvatagem</t>
-  </si>
-  <si>
-    <t>Serviços Comuns de Engenharia</t>
-  </si>
-  <si>
-    <t>Agricultura Familiar</t>
-  </si>
-  <si>
-    <t>EBC</t>
-  </si>
-  <si>
-    <t>Gestão de Frota</t>
-  </si>
-  <si>
-    <t>Jardinagem e Paisagismo</t>
-  </si>
-  <si>
-    <t>Transporte de Bagagem</t>
-  </si>
-  <si>
-    <t>Rede de Esgoto do GptFNB</t>
-  </si>
-  <si>
-    <t>Manutenção de Elevadores</t>
-  </si>
-  <si>
-    <t>Concertina, portão e gradil</t>
-  </si>
-  <si>
-    <t>Cestas Básicas</t>
-  </si>
-  <si>
-    <t>Nova Sede da CFB</t>
-  </si>
-  <si>
-    <t>Telefonia Fixa</t>
-  </si>
-  <si>
-    <t>prestação de serviços de Provedor de Internet</t>
+    <t>aquisição de Periféricos de Informática</t>
+  </si>
+  <si>
+    <t>serviço de Telefonia Fixa</t>
   </si>
   <si>
     <t>Água Mineral para atendimento das demandas do CeIMBra e OM apoiadas</t>
-  </si>
-  <si>
-    <t>Material Permanente de Rancho para atendimento das necessi.....</t>
-  </si>
-  <si>
-    <t>Bebidas não-alcoólicas para atendimento das necessidades do CeIMBra e demais organizações militares apoiadas</t>
-  </si>
-  <si>
-    <t>Serviços de ornamentação, montagem de estruturas e adequação de
-espaços internos e externos</t>
   </si>
   <si>
     <t>Serviços de Montagem e desmontagem de palanques em estrutura
@@ -679,199 +702,206 @@
     <t>Aquisição de material de higiene e limpeza a fim de atender as necessidades dos diversos setores do Comando do 7º Distrito Naval e Órgãos participantes</t>
   </si>
   <si>
-    <t>aquisição de Periféricos de Informática</t>
+    <t>Bebidas não-alcoólicas para atendimento das necessidades do CeIMBra e demais organizações militares apoiadas</t>
+  </si>
+  <si>
+    <t>Serviços de ornamentação, montagem de estruturas e adequação de
+espaços internos e externos</t>
+  </si>
+  <si>
+    <t>prestação de serviços de Provedor de Internet</t>
+  </si>
+  <si>
+    <t>Material Permanente de Rancho para atendimento das necessi.....</t>
   </si>
   <si>
     <t>Aquisição de material de representação</t>
   </si>
   <si>
-    <t>serviço de Telefonia Fixa</t>
+    <t>787010</t>
   </si>
   <si>
     <t>787310</t>
   </si>
   <si>
-    <t>787010</t>
-  </si>
-  <si>
     <t>787000</t>
   </si>
   <si>
+    <t>787200</t>
+  </si>
+  <si>
     <t>787400</t>
   </si>
   <si>
     <t>787320</t>
   </si>
   <si>
-    <t>787200</t>
-  </si>
-  <si>
     <t>787900</t>
   </si>
   <si>
+    <t>CENTRO DE INTENDÊNCIA DA MARINHA EM BRASÍLIA</t>
+  </si>
+  <si>
     <t>CAPITANIA FLUVIAL DE ARAGUAIA-TOCANTINS</t>
   </si>
   <si>
-    <t>CENTRO DE INTENDÊNCIA DA MARINHA EM BRASÍLIA</t>
-  </si>
-  <si>
     <t>COMANDO DO 7º DISTRITO NAVAL</t>
   </si>
   <si>
+    <t>GRUPAMENTO DE FUZILEIROS NAVAIS DE BRASÍLIA</t>
+  </si>
+  <si>
     <t>ESTAÇÃO RÁDIO DA MARINHA EM BRASÍLIA</t>
   </si>
   <si>
     <t>CAPITANIA FLUVIAL DE BRASÍLIA</t>
   </si>
   <si>
-    <t>GRUPAMENTO DE FUZILEIROS NAVAIS DE BRASÍLIA</t>
-  </si>
-  <si>
     <t>CENTRO DE INSTRUÇÃO E ADESTRAMENTO DE BRASÍLIA</t>
   </si>
   <si>
+    <t>CeIMBra</t>
+  </si>
+  <si>
     <t>CFAT</t>
   </si>
   <si>
-    <t>CeIMBra</t>
-  </si>
-  <si>
     <t>Com7ºDN</t>
   </si>
   <si>
+    <t>GptFNB</t>
+  </si>
+  <si>
     <t>ERMB</t>
   </si>
   <si>
     <t>CFB</t>
   </si>
   <si>
-    <t>GptFNB</t>
-  </si>
-  <si>
     <t>CIAB</t>
   </si>
   <si>
+    <t>Divisão de Municiamento</t>
+  </si>
+  <si>
+    <t>Divisão de Abastecimento</t>
+  </si>
+  <si>
+    <t>DEPARTAMENTO DE TECNOLOGIA DA INFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>DIVISÃO DE SAÚDE E EDUCAÇÃO FÍSICA</t>
+  </si>
+  <si>
+    <t>DIVISÃO DE TRANSPORTES</t>
+  </si>
+  <si>
+    <t>Divisão de Serviços Gerais</t>
+  </si>
+  <si>
+    <t>Seção de Requisição de Passagens e Bagagens</t>
+  </si>
+  <si>
+    <t>Divisão de Controle Patrimonial</t>
+  </si>
+  <si>
+    <t>Assessoria de Comunicação Social</t>
+  </si>
+  <si>
+    <t>SPI</t>
+  </si>
+  <si>
     <t>Divisão de Intendência</t>
   </si>
   <si>
-    <t>Divisão de Abastecimento</t>
-  </si>
-  <si>
-    <t>Divisão de Serviços Gerais</t>
-  </si>
-  <si>
-    <t>Divisão de Municiamento</t>
-  </si>
-  <si>
-    <t>Assessoria de Comunicação Social</t>
-  </si>
-  <si>
-    <t>Divisão de Controle Patrimonial</t>
-  </si>
-  <si>
-    <t>SPI</t>
-  </si>
-  <si>
-    <t>DEPARTAMENTO DE TECNOLOGIA DA INFORMAÇÃO</t>
-  </si>
-  <si>
     <t>ASSESSORIA DE COMUNICAÇÃO SOCIAL</t>
   </si>
   <si>
-    <t>DIVISÃO DE SAÚDE E EDUCAÇÃO FÍSICA</t>
-  </si>
-  <si>
-    <t>DIVISÃO DE TRANSPORTES</t>
-  </si>
-  <si>
     <t>DIVISÃO DE TRANSPORTE</t>
   </si>
   <si>
-    <t>Seção de Requisição de Passagens e Bagagens</t>
+    <t>R$ 4.245.297,80</t>
+  </si>
+  <si>
+    <t>R$ 0,00</t>
+  </si>
+  <si>
+    <t>R$ 120.768,00</t>
+  </si>
+  <si>
+    <t>R$ 4.500.025,00</t>
+  </si>
+  <si>
+    <t>R$ 374.823,00</t>
+  </si>
+  <si>
+    <t>R$ 3.916.344,84</t>
+  </si>
+  <si>
+    <t>R$ 2.138.628,37</t>
+  </si>
+  <si>
+    <t>R$ 234.234,00</t>
+  </si>
+  <si>
+    <t>R$ 249.999,00</t>
+  </si>
+  <si>
+    <t>R$ 9.508.413,80</t>
+  </si>
+  <si>
+    <t>R$ 3.096.464,64</t>
+  </si>
+  <si>
+    <t>R$ 1.128.460,00</t>
+  </si>
+  <si>
+    <t>R$ 1.685.509,00</t>
+  </si>
+  <si>
+    <t>R$ 3.436.038,50</t>
   </si>
   <si>
     <t>R$ 325.239,20</t>
   </si>
   <si>
-    <t>R$ 4.500.025,00</t>
-  </si>
-  <si>
-    <t>R$ 2.138.628,37</t>
+    <t>R$ 1.532,00</t>
   </si>
   <si>
     <t>R$ 151.200,00</t>
   </si>
   <si>
+    <t>R$ 3.822.074,00</t>
+  </si>
+  <si>
     <t>R$ 1.040.000,00</t>
   </si>
   <si>
+    <t>R$ 6.747.823,40</t>
+  </si>
+  <si>
     <t>R$ 25.152.088,87</t>
   </si>
   <si>
-    <t>R$ 1.532,00</t>
-  </si>
-  <si>
-    <t>R$ 1.128.460,00</t>
-  </si>
-  <si>
-    <t>R$ 0,00</t>
-  </si>
-  <si>
-    <t>R$ 249.999,00</t>
-  </si>
-  <si>
-    <t>R$ 3.822.074,00</t>
-  </si>
-  <si>
-    <t>R$ 1.685.509,00</t>
-  </si>
-  <si>
-    <t>R$ 3.436.038,50</t>
-  </si>
-  <si>
-    <t>R$ 9.508.413,80</t>
-  </si>
-  <si>
-    <t>R$ 3.916.344,84</t>
-  </si>
-  <si>
-    <t>R$ 3.096.464,64</t>
+    <t>R$ 1.614.627,00</t>
   </si>
   <si>
     <t>R$ 3.577.824,73</t>
   </si>
   <si>
-    <t>R$ 4.245.297,80</t>
+    <t>R$ 1.154.163,00</t>
   </si>
   <si>
     <t>R$ 3.136.514,46</t>
   </si>
   <si>
-    <t>R$ 120.768,00</t>
-  </si>
-  <si>
     <t>R$ 968.774,04</t>
   </si>
   <si>
-    <t>R$ 1.154.163,00</t>
-  </si>
-  <si>
-    <t>R$ 6.747.823,40</t>
-  </si>
-  <si>
-    <t>R$ 1.614.627,00</t>
-  </si>
-  <si>
-    <t>R$ 374.823,00</t>
-  </si>
-  <si>
-    <t>R$ 234.234,00</t>
+    <t>Sim</t>
   </si>
   <si>
     <t>Não</t>
-  </si>
-  <si>
-    <t>Sim</t>
   </si>
 </sst>
 </file>
@@ -1287,46 +1317,46 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G2" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="J2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="L2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M2" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="N2" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="O2" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1334,40 +1364,43 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G3" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="J3" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="K3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="N3" t="s">
-        <v>258</v>
+        <v>268</v>
+      </c>
+      <c r="O3" t="s">
+        <v>294</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1375,137 +1408,134 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="G4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H4" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="J4" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="K4" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="L4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="N4" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="O4" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F5" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G5" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H5" t="s">
-        <v>170</v>
-      </c>
-      <c r="I5" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="J5" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="K5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="L5" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="M5" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="N5" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="O5" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F6" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G6" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="J6" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="K6" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="L6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="N6" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="O6" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1513,43 +1543,49 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F7" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G7" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H7" t="s">
-        <v>172</v>
+        <v>182</v>
+      </c>
+      <c r="I7" t="s">
+        <v>223</v>
       </c>
       <c r="J7" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="K7" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="L7" t="s">
-        <v>238</v>
+        <v>249</v>
+      </c>
+      <c r="M7" t="s">
+        <v>256</v>
       </c>
       <c r="N7" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="O7" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P7">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1557,43 +1593,46 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F8" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H8" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="J8" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K8" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L8" t="s">
-        <v>239</v>
+        <v>249</v>
+      </c>
+      <c r="M8" t="s">
+        <v>257</v>
       </c>
       <c r="N8" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="O8" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P8">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1601,43 +1640,46 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F9" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G9" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="J9" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="K9" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L9" t="s">
-        <v>242</v>
+        <v>249</v>
+      </c>
+      <c r="M9" t="s">
+        <v>258</v>
       </c>
       <c r="N9" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="O9" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P9">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1645,46 +1687,46 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F10" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="G10" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H10" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="J10" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="K10" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="L10" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="M10" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="N10" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O10" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P10">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1692,46 +1734,46 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F11" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G11" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H11" t="s">
-        <v>176</v>
-      </c>
-      <c r="I11" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="J11" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="K11" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="L11" t="s">
-        <v>238</v>
+        <v>247</v>
+      </c>
+      <c r="M11" t="s">
+        <v>254</v>
       </c>
       <c r="N11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O11" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P11">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1739,46 +1781,43 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F12" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G12" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="H12" t="s">
-        <v>177</v>
-      </c>
-      <c r="I12" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="J12" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="K12" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L12" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="N12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O12" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P12">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1786,1171 +1825,1159 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F13" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="G13" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
-        <v>178</v>
+        <v>188</v>
+      </c>
+      <c r="I13" t="s">
+        <v>188</v>
       </c>
       <c r="J13" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="K13" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="L13" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="M13" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="N13" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O13" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="P13">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F14" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="G14" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>179</v>
-      </c>
-      <c r="I14" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="J14" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="K14" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="L14" t="s">
-        <v>238</v>
-      </c>
-      <c r="M14" t="s">
         <v>247</v>
       </c>
       <c r="N14" t="s">
-        <v>268</v>
-      </c>
-      <c r="O14" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="P14">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F15" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G15" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H15" t="s">
-        <v>180</v>
-      </c>
-      <c r="I15" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J15" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K15" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L15" t="s">
-        <v>239</v>
-      </c>
-      <c r="M15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O15" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="P15">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F16" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="G16" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H16" t="s">
-        <v>181</v>
-      </c>
-      <c r="I16" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="J16" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K16" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L16" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M16" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="N16" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O16" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="P16">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F17" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="G17" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H17" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="J17" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K17" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L17" t="s">
-        <v>239</v>
-      </c>
-      <c r="M17" t="s">
         <v>249</v>
       </c>
       <c r="N17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O17" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="P17">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F18" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="G18" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H18" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="I18" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J18" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K18" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L18" t="s">
-        <v>239</v>
-      </c>
-      <c r="M18" t="s">
         <v>249</v>
       </c>
       <c r="N18" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O18" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P18">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F19" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="G19" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H19" t="s">
-        <v>184</v>
+        <v>194</v>
+      </c>
+      <c r="I19" t="s">
+        <v>225</v>
       </c>
       <c r="J19" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="K19" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="L19" t="s">
-        <v>238</v>
-      </c>
-      <c r="M19" t="s">
         <v>247</v>
       </c>
       <c r="N19" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="O19" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="P19">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F20" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G20" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
-        <v>185</v>
+        <v>195</v>
+      </c>
+      <c r="I20" t="s">
+        <v>226</v>
       </c>
       <c r="J20" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K20" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L20" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M20" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="N20" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="O20" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="P20">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F21" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="G21" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H21" t="s">
-        <v>186</v>
+        <v>196</v>
+      </c>
+      <c r="I21" t="s">
+        <v>227</v>
       </c>
       <c r="J21" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K21" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L21" t="s">
-        <v>239</v>
+        <v>249</v>
+      </c>
+      <c r="M21" t="s">
+        <v>261</v>
       </c>
       <c r="N21" t="s">
-        <v>265</v>
+        <v>277</v>
+      </c>
+      <c r="O21" t="s">
+        <v>294</v>
       </c>
       <c r="P21">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F22" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G22" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H22" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="J22" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="K22" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s">
-        <v>239</v>
+        <v>247</v>
+      </c>
+      <c r="M22" t="s">
+        <v>254</v>
       </c>
       <c r="N22" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O22" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P22">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F23" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G23" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H23" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="J23" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="K23" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L23" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="O23" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="P23">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F24" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="G24" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H24" t="s">
-        <v>189</v>
+        <v>199</v>
+      </c>
+      <c r="I24" t="s">
+        <v>228</v>
       </c>
       <c r="J24" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K24" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="L24" t="s">
-        <v>243</v>
+        <v>247</v>
+      </c>
+      <c r="M24" t="s">
+        <v>254</v>
       </c>
       <c r="N24" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="O24" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P24">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F25" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G25" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H25" t="s">
-        <v>190</v>
+        <v>200</v>
+      </c>
+      <c r="I25" t="s">
+        <v>229</v>
       </c>
       <c r="J25" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="K25" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="L25" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="N25" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="O25" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="P25">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="G26" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H26" t="s">
-        <v>191</v>
-      </c>
-      <c r="I26" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="J26" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K26" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O26" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="P26">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F27" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="G27" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H27" t="s">
-        <v>192</v>
-      </c>
-      <c r="I27" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="J27" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="K27" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="L27" t="s">
-        <v>239</v>
-      </c>
-      <c r="M27" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N27" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O27" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="P27">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F28" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="G28" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H28" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="J28" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="K28" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="L28" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="M28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N28" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O28" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="P28">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G29" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H29" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="J29" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="K29" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="M29" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="N29" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="O29" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G30" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H30" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="J30" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K30" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L30" t="s">
-        <v>239</v>
-      </c>
-      <c r="M30" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="N30" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="O30" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F31" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G31" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H31" t="s">
-        <v>196</v>
+        <v>206</v>
+      </c>
+      <c r="I31" t="s">
+        <v>230</v>
       </c>
       <c r="J31" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="K31" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="L31" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N31" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="O31" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="P31">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F32" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G32" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H32" t="s">
-        <v>197</v>
+        <v>207</v>
+      </c>
+      <c r="I32" t="s">
+        <v>231</v>
       </c>
       <c r="J32" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="K32" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="L32" t="s">
-        <v>238</v>
-      </c>
-      <c r="M32" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N32" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="O32" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="P32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E33" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="G33" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H33" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="J33" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="K33" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="L33" t="s">
-        <v>238</v>
-      </c>
-      <c r="M33" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N33" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="O33" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="P33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E34" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F34" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G34" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H34" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="J34" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="K34" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="L34" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="M34" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="N34" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="O34" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="P34">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E35" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F35" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G35" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H35" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="J35" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="K35" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="L35" t="s">
-        <v>239</v>
-      </c>
-      <c r="M35" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N35" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O35" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="P35">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E36" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F36" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="G36" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H36" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="J36" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="K36" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="L36" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="M36" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="N36" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O36" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="P36">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D37" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F37" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G37" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H37" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="J37" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="K37" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="L37" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="N37" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="O37" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P37">
         <v>9</v>
@@ -2958,43 +2985,43 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="E38" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F38" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="G38" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H38" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="J38" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="K38" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="L38" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="N38" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="O38" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P38">
         <v>9</v>
@@ -3002,43 +3029,46 @@
     </row>
     <row r="39" spans="1:16">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C39" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="E39" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F39" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G39" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H39" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="J39" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="K39" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="L39" t="s">
-        <v>238</v>
+        <v>249</v>
+      </c>
+      <c r="M39" t="s">
+        <v>259</v>
       </c>
       <c r="N39" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="O39" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P39">
         <v>9</v>
@@ -3046,46 +3076,49 @@
     </row>
     <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E40" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G40" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H40" t="s">
-        <v>204</v>
+        <v>215</v>
+      </c>
+      <c r="I40" t="s">
+        <v>232</v>
       </c>
       <c r="J40" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K40" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L40" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M40" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="N40" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O40" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P40">
         <v>9</v>
@@ -3093,43 +3126,46 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E41" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F41" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G41" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="H41" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="J41" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="K41" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="L41" t="s">
-        <v>239</v>
+        <v>247</v>
+      </c>
+      <c r="M41" t="s">
+        <v>254</v>
       </c>
       <c r="N41" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="O41" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P41">
         <v>9</v>
@@ -3137,49 +3173,46 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E42" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F42" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G42" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H42" t="s">
-        <v>206</v>
-      </c>
-      <c r="I42" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="J42" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="K42" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="L42" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="M42" t="s">
         <v>256</v>
       </c>
       <c r="N42" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O42" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P42">
         <v>9</v>
@@ -3187,46 +3220,43 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C43" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E43" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F43" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G43" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H43" t="s">
-        <v>207</v>
-      </c>
-      <c r="I43" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="J43" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="K43" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L43" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="N43" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="O43" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P43">
         <v>9</v>
@@ -3234,178 +3264,181 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E44" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F44" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G44" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H44" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J44" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="K44" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="L44" t="s">
-        <v>239</v>
+        <v>247</v>
+      </c>
+      <c r="M44" t="s">
+        <v>254</v>
       </c>
       <c r="N44" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="O44" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P44">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E45" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F45" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="G45" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H45" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="J45" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="K45" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="L45" t="s">
-        <v>240</v>
-      </c>
-      <c r="M45" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="N45" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="O45" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="P45">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C46" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E46" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F46" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G46" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H46" t="s">
-        <v>210</v>
+        <v>219</v>
+      </c>
+      <c r="I46" t="s">
+        <v>219</v>
       </c>
       <c r="J46" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="K46" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="L46" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="N46" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="O46" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P46">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C47" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D47" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="E47" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F47" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G47" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H47" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J47" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="K47" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="L47" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="N47" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="O47" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="P47">
         <v>10</v>
@@ -3413,46 +3446,46 @@
     </row>
     <row r="48" spans="1:16">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D48" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E48" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F48" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G48" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H48" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="J48" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="K48" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="L48" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="M48" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="N48" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="O48" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="P48">
         <v>10</v>
@@ -3460,93 +3493,90 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D49" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E49" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F49" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G49" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H49" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="J49" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K49" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L49" t="s">
-        <v>239</v>
+        <v>249</v>
+      </c>
+      <c r="M49" t="s">
+        <v>266</v>
       </c>
       <c r="N49" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="O49" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="P49">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C50" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D50" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E50" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F50" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G50" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H50" t="s">
-        <v>212</v>
-      </c>
-      <c r="I50" t="s">
         <v>222</v>
       </c>
       <c r="J50" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K50" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L50" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="N50" t="s">
-        <v>282</v>
-      </c>
-      <c r="O50" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="P50">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/tabela_completa.xlsx
+++ b/tabela_completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="351">
   <si>
     <t>situacao</t>
   </si>
@@ -64,10 +64,10 @@
     <t>order</t>
   </si>
   <si>
-    <t>Pré-Publicação</t>
-  </si>
-  <si>
-    <t>Recomendações AGU</t>
+    <t>Assinatura Contrato</t>
+  </si>
+  <si>
+    <t>Sessão Pública</t>
   </si>
   <si>
     <t>AGU</t>
@@ -91,607 +91,748 @@
     <t>Concluído</t>
   </si>
   <si>
-    <t>Arquivado</t>
+    <t>PE 90012/2024</t>
+  </si>
+  <si>
+    <t>PE 90005/2025</t>
+  </si>
+  <si>
+    <t>PE 90020/2024</t>
+  </si>
+  <si>
+    <t>TJDL 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90019/2024</t>
+  </si>
+  <si>
+    <t>PE 90028/2024</t>
   </si>
   <si>
     <t>PE 90031/2024</t>
   </si>
   <si>
+    <t>PE 90039/2024</t>
+  </si>
+  <si>
+    <t>PE 04/2023</t>
+  </si>
+  <si>
+    <t>PE 07/2023</t>
+  </si>
+  <si>
+    <t>PE 08/2023</t>
+  </si>
+  <si>
+    <t>PE 10/2023</t>
+  </si>
+  <si>
+    <t>PE 13/2023</t>
+  </si>
+  <si>
+    <t>PE 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90011/2024</t>
+  </si>
+  <si>
+    <t>PE 90027/2024</t>
+  </si>
+  <si>
+    <t>PE 90030/2024</t>
+  </si>
+  <si>
+    <t>PE 90032/2024</t>
+  </si>
+  <si>
+    <t>CC 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90008/2024</t>
+  </si>
+  <si>
+    <t>PE 90010/2024</t>
+  </si>
+  <si>
+    <t>PE 90013/2024</t>
+  </si>
+  <si>
+    <t>PE 90036/2024</t>
+  </si>
+  <si>
+    <t>PE 90040/2024</t>
+  </si>
+  <si>
+    <t>PE 90002/2024</t>
+  </si>
+  <si>
+    <t>PE 90003/2024</t>
+  </si>
+  <si>
+    <t>PE 90004/2024</t>
+  </si>
+  <si>
+    <t>PE 90005/2024</t>
+  </si>
+  <si>
+    <t>PE 90006/2024</t>
+  </si>
+  <si>
+    <t>PE 90007/2024</t>
+  </si>
+  <si>
+    <t>PE 90009/2024</t>
+  </si>
+  <si>
+    <t>PE 90014/2024</t>
+  </si>
+  <si>
+    <t>PE 90015/2024</t>
+  </si>
+  <si>
+    <t>PE 90016/2024</t>
+  </si>
+  <si>
+    <t>PE 90017/2024</t>
+  </si>
+  <si>
+    <t>PE 90018/2024</t>
+  </si>
+  <si>
+    <t>PE 90021/2024</t>
+  </si>
+  <si>
+    <t>PE 90022/2024</t>
+  </si>
+  <si>
+    <t>PE 90023/2024</t>
+  </si>
+  <si>
+    <t>PE 90025/2024</t>
+  </si>
+  <si>
+    <t>PE 90026/2024</t>
+  </si>
+  <si>
+    <t>PE 90029/2024</t>
+  </si>
+  <si>
+    <t>PE 90033/2024</t>
+  </si>
+  <si>
     <t>PE 90044/2024</t>
   </si>
   <si>
     <t>TJIL 90001/2024</t>
   </si>
   <si>
-    <t>PE 90002/2024</t>
-  </si>
-  <si>
-    <t>PE 90019/2024</t>
-  </si>
-  <si>
-    <t>PE 90023/2024</t>
-  </si>
-  <si>
-    <t>PE 90025/2024</t>
-  </si>
-  <si>
-    <t>PE 90026/2024</t>
-  </si>
-  <si>
-    <t>PE 90027/2024</t>
-  </si>
-  <si>
-    <t>PE 90028/2024</t>
-  </si>
-  <si>
-    <t>PE 90036/2024</t>
+    <t>PE 90035/2024</t>
   </si>
   <si>
     <t>PE 90037/2024</t>
   </si>
   <si>
-    <t>PE 08/2023</t>
-  </si>
-  <si>
-    <t>PE 90004/2024</t>
-  </si>
-  <si>
-    <t>PE 90014/2024</t>
-  </si>
-  <si>
-    <t>PE 10/2023</t>
-  </si>
-  <si>
-    <t>PE 90006/2024</t>
-  </si>
-  <si>
-    <t>PE 90007/2024</t>
-  </si>
-  <si>
-    <t>PE 90013/2024</t>
-  </si>
-  <si>
-    <t>PE 90015/2024</t>
-  </si>
-  <si>
-    <t>PE 90016/2024</t>
-  </si>
-  <si>
-    <t>PE 90001/2024</t>
-  </si>
-  <si>
-    <t>PE 90011/2024</t>
-  </si>
-  <si>
-    <t>PE 90012/2024</t>
-  </si>
-  <si>
-    <t>PE 90017/2024</t>
-  </si>
-  <si>
-    <t>PE 90020/2024</t>
-  </si>
-  <si>
-    <t>PE 90033/2024</t>
-  </si>
-  <si>
-    <t>PE 07/2023</t>
-  </si>
-  <si>
-    <t>PE 13/2023</t>
-  </si>
-  <si>
-    <t>PE 90005/2024</t>
-  </si>
-  <si>
-    <t>PE 90008/2024</t>
-  </si>
-  <si>
-    <t>PE 90009/2024</t>
-  </si>
-  <si>
-    <t>PE 90010/2024</t>
-  </si>
-  <si>
-    <t>PE 90021/2024</t>
-  </si>
-  <si>
-    <t>PE 90022/2024</t>
-  </si>
-  <si>
-    <t>CC 90001/2024</t>
-  </si>
-  <si>
-    <t>PE 04/2023</t>
-  </si>
-  <si>
-    <t>PE 90003/2024</t>
+    <t>PE 90038/2024</t>
+  </si>
+  <si>
+    <t>PE 90041/2024</t>
+  </si>
+  <si>
+    <t>PE 90049/2024</t>
+  </si>
+  <si>
+    <t>PE 90050/2024</t>
+  </si>
+  <si>
+    <t>PE 90052/2024</t>
+  </si>
+  <si>
+    <t>PE 90053/2024</t>
+  </si>
+  <si>
+    <t>PE 90054/2024</t>
+  </si>
+  <si>
+    <t>PE 90055/2023</t>
+  </si>
+  <si>
+    <t>PE 90056/2024</t>
+  </si>
+  <si>
+    <t>PE 90057/2024</t>
+  </si>
+  <si>
+    <t>PE 90058/2024</t>
+  </si>
+  <si>
+    <t>PE 90059/2024</t>
+  </si>
+  <si>
+    <t>PE 90060/2024</t>
+  </si>
+  <si>
+    <t>PE 90061/2024</t>
+  </si>
+  <si>
+    <t>PE 90062/2024</t>
+  </si>
+  <si>
+    <t>PE 90063/2024</t>
+  </si>
+  <si>
+    <t>PE 90064/2024</t>
+  </si>
+  <si>
+    <t>PE 90065/2024</t>
+  </si>
+  <si>
+    <t>PE 1/2025</t>
+  </si>
+  <si>
+    <t>PE 2/2025</t>
+  </si>
+  <si>
+    <t>PE 3/2025</t>
   </si>
   <si>
     <t>PE 90024/2024</t>
   </si>
   <si>
-    <t>PE 90029/2024</t>
-  </si>
-  <si>
-    <t>PE 90032/2024</t>
-  </si>
-  <si>
-    <t>PE 90041/2024</t>
-  </si>
-  <si>
-    <t>PE 90030/2024</t>
-  </si>
-  <si>
-    <t>TJDL 90001/2024</t>
-  </si>
-  <si>
-    <t>PE 90038/2024</t>
-  </si>
-  <si>
-    <t>PE 90039/2024</t>
-  </si>
-  <si>
-    <t>PE 90040/2024</t>
-  </si>
-  <si>
-    <t>PE 90035/2024</t>
-  </si>
-  <si>
-    <t>PE 90018/2024</t>
-  </si>
-  <si>
     <t>Pregão Eletrônico</t>
   </si>
   <si>
+    <t>Termo de Justificativa para Dispensa de Licitação</t>
+  </si>
+  <si>
+    <t>Concorrência</t>
+  </si>
+  <si>
     <t>Termo de Justificativa para Inexigibilidade de Licitação</t>
   </si>
   <si>
-    <t>Concorrência</t>
-  </si>
-  <si>
-    <t>Termo de Justificativa para Dispensa de Licitação</t>
+    <t>90012</t>
+  </si>
+  <si>
+    <t>90005</t>
+  </si>
+  <si>
+    <t>90020</t>
+  </si>
+  <si>
+    <t>90001</t>
+  </si>
+  <si>
+    <t>90019</t>
+  </si>
+  <si>
+    <t>90028</t>
   </si>
   <si>
     <t>90031</t>
   </si>
   <si>
+    <t>90039</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>90011</t>
+  </si>
+  <si>
+    <t>90027</t>
+  </si>
+  <si>
+    <t>90030</t>
+  </si>
+  <si>
+    <t>90032</t>
+  </si>
+  <si>
+    <t>90008</t>
+  </si>
+  <si>
+    <t>90010</t>
+  </si>
+  <si>
+    <t>90013</t>
+  </si>
+  <si>
+    <t>90036</t>
+  </si>
+  <si>
+    <t>90040</t>
+  </si>
+  <si>
+    <t>90002</t>
+  </si>
+  <si>
+    <t>90003</t>
+  </si>
+  <si>
+    <t>90004</t>
+  </si>
+  <si>
+    <t>90006</t>
+  </si>
+  <si>
+    <t>90007</t>
+  </si>
+  <si>
+    <t>90009</t>
+  </si>
+  <si>
+    <t>90014</t>
+  </si>
+  <si>
+    <t>90015</t>
+  </si>
+  <si>
+    <t>90016</t>
+  </si>
+  <si>
+    <t>90017</t>
+  </si>
+  <si>
+    <t>90018</t>
+  </si>
+  <si>
+    <t>90021</t>
+  </si>
+  <si>
+    <t>90022</t>
+  </si>
+  <si>
+    <t>90023</t>
+  </si>
+  <si>
+    <t>90025</t>
+  </si>
+  <si>
+    <t>90026</t>
+  </si>
+  <si>
+    <t>90029</t>
+  </si>
+  <si>
+    <t>90033</t>
+  </si>
+  <si>
     <t>90044</t>
   </si>
   <si>
-    <t>90001</t>
-  </si>
-  <si>
-    <t>90002</t>
-  </si>
-  <si>
-    <t>90019</t>
-  </si>
-  <si>
-    <t>90023</t>
-  </si>
-  <si>
-    <t>90025</t>
-  </si>
-  <si>
-    <t>90026</t>
-  </si>
-  <si>
-    <t>90027</t>
-  </si>
-  <si>
-    <t>90028</t>
-  </si>
-  <si>
-    <t>90036</t>
+    <t>90035</t>
   </si>
   <si>
     <t>90037</t>
   </si>
   <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>90004</t>
-  </si>
-  <si>
-    <t>90014</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>90006</t>
-  </si>
-  <si>
-    <t>90007</t>
-  </si>
-  <si>
-    <t>90013</t>
-  </si>
-  <si>
-    <t>90015</t>
-  </si>
-  <si>
-    <t>90016</t>
-  </si>
-  <si>
-    <t>90011</t>
-  </si>
-  <si>
-    <t>90012</t>
-  </si>
-  <si>
-    <t>90017</t>
-  </si>
-  <si>
-    <t>90020</t>
-  </si>
-  <si>
-    <t>90033</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>90005</t>
-  </si>
-  <si>
-    <t>90008</t>
-  </si>
-  <si>
-    <t>90009</t>
-  </si>
-  <si>
-    <t>90010</t>
-  </si>
-  <si>
-    <t>90021</t>
-  </si>
-  <si>
-    <t>90022</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>90003</t>
+    <t>90038</t>
+  </si>
+  <si>
+    <t>90041</t>
+  </si>
+  <si>
+    <t>90049</t>
+  </si>
+  <si>
+    <t>90050</t>
+  </si>
+  <si>
+    <t>90052</t>
+  </si>
+  <si>
+    <t>90053</t>
+  </si>
+  <si>
+    <t>90054</t>
+  </si>
+  <si>
+    <t>90055</t>
+  </si>
+  <si>
+    <t>90056</t>
+  </si>
+  <si>
+    <t>90057</t>
+  </si>
+  <si>
+    <t>90058</t>
+  </si>
+  <si>
+    <t>90059</t>
+  </si>
+  <si>
+    <t>90060</t>
+  </si>
+  <si>
+    <t>90061</t>
+  </si>
+  <si>
+    <t>90062</t>
+  </si>
+  <si>
+    <t>90063</t>
+  </si>
+  <si>
+    <t>90064</t>
+  </si>
+  <si>
+    <t>90065</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>90024</t>
   </si>
   <si>
-    <t>90029</t>
-  </si>
-  <si>
-    <t>90032</t>
-  </si>
-  <si>
-    <t>90041</t>
-  </si>
-  <si>
-    <t>90030</t>
-  </si>
-  <si>
-    <t>90038</t>
-  </si>
-  <si>
-    <t>90039</t>
-  </si>
-  <si>
-    <t>90040</t>
-  </si>
-  <si>
-    <t>90035</t>
-  </si>
-  <si>
-    <t>90018</t>
-  </si>
-  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
+    <t>63402.000286/2024-04</t>
+  </si>
+  <si>
+    <t>63402.000359/2024-50</t>
+  </si>
+  <si>
+    <t>63402.000403/2024-21</t>
+  </si>
+  <si>
+    <t>63402.000360/2024-84</t>
+  </si>
+  <si>
+    <t>63402.000321/2024-87</t>
+  </si>
+  <si>
     <t>63402.000332/2024-67</t>
   </si>
   <si>
+    <t>63402.000907/2024-41</t>
+  </si>
+  <si>
+    <t>62055.000344/2023-35</t>
+  </si>
+  <si>
+    <t>62055.002424/2023-25</t>
+  </si>
+  <si>
+    <t>62055.002426/2023-14</t>
+  </si>
+  <si>
+    <t>62055.002463/2023-22</t>
+  </si>
+  <si>
+    <t>63402.000326/2024-18</t>
+  </si>
+  <si>
+    <t>63402.000324/2024-11</t>
+  </si>
+  <si>
+    <t>63402.000320/2024-32</t>
+  </si>
+  <si>
+    <t>63402.000322/2024-21</t>
+  </si>
+  <si>
+    <t>63402.000800/2024-01</t>
+  </si>
+  <si>
+    <t>63402.000318/2024-63</t>
+  </si>
+  <si>
+    <t>63402.000314/2024-85</t>
+  </si>
+  <si>
+    <t>63402.000289/2024-30</t>
+  </si>
+  <si>
+    <t>63402.000750/2024-54</t>
+  </si>
+  <si>
+    <t>63402.000915/2024-98</t>
+  </si>
+  <si>
+    <t>63402.000338/2024-34</t>
+  </si>
+  <si>
+    <t>63402.000312/2024-96</t>
+  </si>
+  <si>
+    <t>63402.000334/2024-56</t>
+  </si>
+  <si>
+    <t>63402.000330/2024-78</t>
+  </si>
+  <si>
+    <t>63402.000328/2024-07</t>
+  </si>
+  <si>
+    <t>63402.000331/2024-12</t>
+  </si>
+  <si>
+    <t>63402.000313/2024-31</t>
+  </si>
+  <si>
+    <t>63402.000315/2024-20</t>
+  </si>
+  <si>
+    <t>63402.000316/2024-74</t>
+  </si>
+  <si>
+    <t>63402.000319/2024-16</t>
+  </si>
+  <si>
+    <t>63402.000317/2024-19</t>
+  </si>
+  <si>
+    <t>63402.000352/2024-38</t>
+  </si>
+  <si>
+    <t>63402.000358/2024-13</t>
+  </si>
+  <si>
+    <t>63402.000357/2024-61</t>
+  </si>
+  <si>
+    <t>63402.000355/2024-71</t>
+  </si>
+  <si>
+    <t>63402.000361/2024-69</t>
+  </si>
+  <si>
+    <t>63402.000325/2024-65</t>
+  </si>
+  <si>
+    <t>63402.000333/2024-10</t>
+  </si>
+  <si>
+    <t>63402.000362/2024-73</t>
+  </si>
+  <si>
     <t>63402.000327/2024-54</t>
   </si>
   <si>
     <t>62055.000130/2024-40</t>
   </si>
   <si>
-    <t>63402.000338/2024-34</t>
-  </si>
-  <si>
-    <t>63402.000360/2024-84</t>
-  </si>
-  <si>
-    <t>63402.000355/2024-71</t>
-  </si>
-  <si>
-    <t>63402.000361/2024-69</t>
-  </si>
-  <si>
-    <t>63402.000325/2024-65</t>
-  </si>
-  <si>
-    <t>63402.000324/2024-11</t>
-  </si>
-  <si>
-    <t>63402.000321/2024-87</t>
-  </si>
-  <si>
-    <t>63402.000750/2024-54</t>
+    <t>63402.000702/2024-66</t>
   </si>
   <si>
     <t>63402.000766/2024-67</t>
   </si>
   <si>
-    <t>62055.002424/2023-25</t>
-  </si>
-  <si>
-    <t>63402.000334/2024-56</t>
-  </si>
-  <si>
-    <t>63402.000315/2024-20</t>
-  </si>
-  <si>
-    <t>62055.002426/2023-14</t>
-  </si>
-  <si>
-    <t>63402.000328/2024-07</t>
-  </si>
-  <si>
-    <t>63402.000331/2024-12</t>
-  </si>
-  <si>
-    <t>63402.000289/2024-30</t>
-  </si>
-  <si>
-    <t>63402.000316/2024-74</t>
-  </si>
-  <si>
-    <t>63402.000319/2024-16</t>
-  </si>
-  <si>
-    <t>62055.002463/2023-22</t>
-  </si>
-  <si>
-    <t>63402.000326/2024-18</t>
-  </si>
-  <si>
-    <t>63402.000286/2024-04</t>
-  </si>
-  <si>
-    <t>63402.000317/2024-19</t>
-  </si>
-  <si>
-    <t>63402.000359/2024-50</t>
-  </si>
-  <si>
-    <t>63402.000362/2024-73</t>
-  </si>
-  <si>
-    <t>63402.000330/2024-78</t>
-  </si>
-  <si>
-    <t>63402.000318/2024-63</t>
-  </si>
-  <si>
-    <t>63402.000313/2024-31</t>
-  </si>
-  <si>
-    <t>63402.000314/2024-85</t>
-  </si>
-  <si>
-    <t>63402.000358/2024-13</t>
-  </si>
-  <si>
-    <t>63402.000357/2024-61</t>
-  </si>
-  <si>
-    <t>63402.000800/2024-01</t>
-  </si>
-  <si>
-    <t>62055.000344/2023-35</t>
-  </si>
-  <si>
-    <t>63402.000312/2024-96</t>
+    <t>63402.000881/2024-31</t>
+  </si>
+  <si>
+    <t>63402.001090/2024-29</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
   <si>
     <t>63402.000354/2024-27</t>
   </si>
   <si>
-    <t>63402.000333/2024-10</t>
-  </si>
-  <si>
-    <t>63402.000322/2024-21</t>
-  </si>
-  <si>
-    <t>63402.001090/2024-29</t>
-  </si>
-  <si>
-    <t>63402.000320/2024-32</t>
-  </si>
-  <si>
-    <t>63402.000403/2024-21</t>
-  </si>
-  <si>
-    <t>63402.000881/2024-31</t>
-  </si>
-  <si>
-    <t>63402.000907/2024-41</t>
-  </si>
-  <si>
-    <t>63402.000915/2024-98</t>
-  </si>
-  <si>
-    <t>63402.000702/2024-66</t>
-  </si>
-  <si>
-    <t>63402.000352/2024-38</t>
+    <t>Serviço</t>
   </si>
   <si>
     <t>material</t>
   </si>
   <si>
+    <t>Material</t>
+  </si>
+  <si>
     <t>servico</t>
   </si>
   <si>
-    <t>Serviço</t>
+    <t>(Renumerado 90066/2024) Serviços de Ornamentação</t>
+  </si>
+  <si>
+    <t>Serviços de Ornamentação</t>
+  </si>
+  <si>
+    <t>Material Esportivo (PROFESP)</t>
+  </si>
+  <si>
+    <t>Agricultura Familiar</t>
+  </si>
+  <si>
+    <t>Material de Segurança Orgânica</t>
+  </si>
+  <si>
+    <t>(Renumerado 90065/2024) Gêneros Frigorificados</t>
   </si>
   <si>
     <t>Gêneros Laticínios e Frios</t>
   </si>
   <si>
+    <t>Manutenção de Elevadores</t>
+  </si>
+  <si>
+    <t>Gêneros Secos</t>
+  </si>
+  <si>
+    <t>Frigorificados – CFAT</t>
+  </si>
+  <si>
+    <t>Panificados</t>
+  </si>
+  <si>
+    <t>Material Elétrico e Eletrônico</t>
+  </si>
+  <si>
+    <t>Material de Pintura</t>
+  </si>
+  <si>
+    <t>(Renumerado 90066/2024) Gás Liquefeito de Petróleo (GLP)</t>
+  </si>
+  <si>
+    <t>Bebidas não-alcoólicas</t>
+  </si>
+  <si>
+    <t>Material Hidráulico</t>
+  </si>
+  <si>
+    <t>Equipamento de Informática</t>
+  </si>
+  <si>
+    <t>Nova Sede da CFB</t>
+  </si>
+  <si>
+    <t>(Renumerado 90066/2024) Material Permanente de Rancho</t>
+  </si>
+  <si>
+    <t>Material de Carpintaria</t>
+  </si>
+  <si>
+    <t>Montagem de Palanque</t>
+  </si>
+  <si>
+    <t>Jardinagem e Paisagismo</t>
+  </si>
+  <si>
+    <t>Concertina, portão e gradil</t>
+  </si>
+  <si>
+    <t>Transporte de Carga</t>
+  </si>
+  <si>
+    <t>Cestas Básicas</t>
+  </si>
+  <si>
+    <t>Provedor de Internet</t>
+  </si>
+  <si>
+    <t>Telefonia Fixa</t>
+  </si>
+  <si>
+    <t>Água Mineral</t>
+  </si>
+  <si>
+    <t>Moto Aquática</t>
+  </si>
+  <si>
+    <t>Material de Expediente</t>
+  </si>
+  <si>
+    <t>Material de Higiene e Limpeza</t>
+  </si>
+  <si>
+    <t>Material para Copa e Cozinha</t>
+  </si>
+  <si>
+    <t>Pisos e Revestimentos</t>
+  </si>
+  <si>
+    <t>Transporte de Pessoal</t>
+  </si>
+  <si>
+    <t>Serviços Gráficos Especializados</t>
+  </si>
+  <si>
+    <t>Mobiliários Corporativos</t>
+  </si>
+  <si>
+    <t>Periféricos de Informática</t>
+  </si>
+  <si>
+    <t>Material de Academia</t>
+  </si>
+  <si>
+    <t>Seguro de Viaturas</t>
+  </si>
+  <si>
+    <t>Gêneros Hortifrutigranjeiros</t>
+  </si>
+  <si>
+    <t>Marinharia e Salvatagem</t>
+  </si>
+  <si>
     <t>Serviços Comuns de Engenharia</t>
   </si>
   <si>
     <t>EBC</t>
   </si>
   <si>
-    <t>Transporte de Carga</t>
-  </si>
-  <si>
-    <t>Material de Segurança Orgânica</t>
-  </si>
-  <si>
-    <t>Periféricos de Informática</t>
-  </si>
-  <si>
-    <t>Material de Academia</t>
-  </si>
-  <si>
-    <t>Seguro de Viaturas</t>
-  </si>
-  <si>
-    <t>Material Hidráulico</t>
+    <t>(Renumerado 1/2025) Gestão de Frota</t>
+  </si>
+  <si>
+    <t>Transporte de Bagagem</t>
+  </si>
+  <si>
+    <t>Rede de Esgoto do GptFNB</t>
+  </si>
+  <si>
+    <t>TESTE</t>
+  </si>
+  <si>
+    <t>Material Permanente de Rancho</t>
   </si>
   <si>
     <t>Gêneros Frigorificados</t>
   </si>
   <si>
-    <t>Jardinagem e Paisagismo</t>
-  </si>
-  <si>
-    <t>Transporte de Bagagem</t>
-  </si>
-  <si>
-    <t>Panificados</t>
-  </si>
-  <si>
-    <t>Cestas Básicas</t>
-  </si>
-  <si>
-    <t>Material de Expediente</t>
-  </si>
-  <si>
-    <t>Material Elétrico e Eletrônico</t>
-  </si>
-  <si>
-    <t>Telefonia Fixa</t>
-  </si>
-  <si>
-    <t>Água Mineral</t>
-  </si>
-  <si>
-    <t>Montagem de Palanque</t>
-  </si>
-  <si>
-    <t>Material de Higiene e Limpeza</t>
-  </si>
-  <si>
-    <t>Material para Copa e Cozinha</t>
+    <t>Gestão de Frota</t>
+  </si>
+  <si>
+    <t>Teste Creni</t>
   </si>
   <si>
     <t>Gás Liquefeito de Petróleo (GLP)</t>
   </si>
   <si>
-    <t>Bebidas não-alcoólicas</t>
-  </si>
-  <si>
-    <t>Serviços de Ornamentação</t>
-  </si>
-  <si>
-    <t>Pisos e Revestimentos</t>
-  </si>
-  <si>
-    <t>Material Esportivo (PROFESP)</t>
-  </si>
-  <si>
-    <t>Marinharia e Salvatagem</t>
-  </si>
-  <si>
-    <t>Frigorificados – CFAT</t>
-  </si>
-  <si>
-    <t>Material de Pintura</t>
-  </si>
-  <si>
-    <t>Provedor de Internet</t>
-  </si>
-  <si>
-    <t>Material Permanente de Rancho</t>
-  </si>
-  <si>
-    <t>Moto Aquática</t>
-  </si>
-  <si>
-    <t>Material de Carpintaria</t>
-  </si>
-  <si>
-    <t>Serviços Gráficos Especializados</t>
-  </si>
-  <si>
-    <t>Mobiliários Corporativos</t>
-  </si>
-  <si>
-    <t>Nova Sede da CFB</t>
-  </si>
-  <si>
-    <t>Gêneros Secos</t>
-  </si>
-  <si>
-    <t>Manutenção de Elevadores</t>
-  </si>
-  <si>
     <t>Material de Representação</t>
   </si>
   <si>
-    <t>Gêneros Hortifrutigranjeiros</t>
-  </si>
-  <si>
-    <t>Equipamento de Informática</t>
-  </si>
-  <si>
-    <t>Agricultura Familiar</t>
-  </si>
-  <si>
-    <t>Rede de Esgoto do GptFNB</t>
-  </si>
-  <si>
-    <t>Concertina, portão e gradil</t>
-  </si>
-  <si>
-    <t>Gestão de Frota</t>
-  </si>
-  <si>
-    <t>Transporte de Pessoal</t>
-  </si>
-  <si>
-    <t>aquisição de Periféricos de Informática</t>
-  </si>
-  <si>
-    <t>serviço de Telefonia Fixa</t>
-  </si>
-  <si>
-    <t>Água Mineral para atendimento das demandas do CeIMBra e OM apoiadas</t>
+    <t>Material Permanente de Rancho para atendimento das necessi.....</t>
   </si>
   <si>
     <t>Serviços de Montagem e desmontagem de palanques em estrutura
@@ -699,95 +840,109 @@
 elétricos e banheiros químicos</t>
   </si>
   <si>
+    <t>prestação de serviços de Provedor de Internet</t>
+  </si>
+  <si>
+    <t>serviço de Telefonia Fixa</t>
+  </si>
+  <si>
+    <t>Água Mineral para atendimento das demandas do CeIMBra e OM apoiadas</t>
+  </si>
+  <si>
     <t>Aquisição de material de higiene e limpeza a fim de atender as necessidades dos diversos setores do Comando do 7º Distrito Naval e Órgãos participantes</t>
   </si>
   <si>
-    <t>Bebidas não-alcoólicas para atendimento das necessidades do CeIMBra e demais organizações militares apoiadas</t>
-  </si>
-  <si>
-    <t>Serviços de ornamentação, montagem de estruturas e adequação de
-espaços internos e externos</t>
-  </si>
-  <si>
-    <t>prestação de serviços de Provedor de Internet</t>
-  </si>
-  <si>
-    <t>Material Permanente de Rancho para atendimento das necessi.....</t>
+    <t>aquisição de Periféricos de Informática</t>
   </si>
   <si>
     <t>Aquisição de material de representação</t>
   </si>
   <si>
+    <t>787000</t>
+  </si>
+  <si>
+    <t>787400</t>
+  </si>
+  <si>
     <t>787010</t>
   </si>
   <si>
     <t>787310</t>
   </si>
   <si>
-    <t>787000</t>
-  </si>
-  <si>
     <t>787200</t>
   </si>
   <si>
-    <t>787400</t>
-  </si>
-  <si>
     <t>787320</t>
   </si>
   <si>
     <t>787900</t>
   </si>
   <si>
+    <t>COMANDO DO 7º DISTRITO NAVAL</t>
+  </si>
+  <si>
+    <t>ESTAÇÃO RÁDIO DA MARINHA EM BRASÍLIA</t>
+  </si>
+  <si>
     <t>CENTRO DE INTENDÊNCIA DA MARINHA EM BRASÍLIA</t>
   </si>
   <si>
     <t>CAPITANIA FLUVIAL DE ARAGUAIA-TOCANTINS</t>
   </si>
   <si>
-    <t>COMANDO DO 7º DISTRITO NAVAL</t>
-  </si>
-  <si>
     <t>GRUPAMENTO DE FUZILEIROS NAVAIS DE BRASÍLIA</t>
   </si>
   <si>
-    <t>ESTAÇÃO RÁDIO DA MARINHA EM BRASÍLIA</t>
-  </si>
-  <si>
     <t>CAPITANIA FLUVIAL DE BRASÍLIA</t>
   </si>
   <si>
     <t>CENTRO DE INSTRUÇÃO E ADESTRAMENTO DE BRASÍLIA</t>
   </si>
   <si>
+    <t>Com7ºDN</t>
+  </si>
+  <si>
+    <t>ERMB</t>
+  </si>
+  <si>
     <t>CeIMBra</t>
   </si>
   <si>
     <t>CFAT</t>
   </si>
   <si>
-    <t>Com7ºDN</t>
-  </si>
-  <si>
     <t>GptFNB</t>
   </si>
   <si>
-    <t>ERMB</t>
-  </si>
-  <si>
     <t>CFB</t>
   </si>
   <si>
     <t>CIAB</t>
   </si>
   <si>
+    <t>Assessoria de Comunicação Social</t>
+  </si>
+  <si>
     <t>Divisão de Municiamento</t>
   </si>
   <si>
+    <t>Divisão de Serviços Gerais</t>
+  </si>
+  <si>
+    <t>DEPARTAMENTO DE TECNOLOGIA DA INFORMAÇÃO</t>
+  </si>
+  <si>
     <t>Divisão de Abastecimento</t>
   </si>
   <si>
-    <t>DEPARTAMENTO DE TECNOLOGIA DA INFORMAÇÃO</t>
+    <t>Divisão de Intendência</t>
+  </si>
+  <si>
+    <t>Divisão de Controle Patrimonial</t>
+  </si>
+  <si>
+    <t>SPI</t>
   </si>
   <si>
     <t>DIVISÃO DE SAÚDE E EDUCAÇÃO FÍSICA</t>
@@ -796,112 +951,124 @@
     <t>DIVISÃO DE TRANSPORTES</t>
   </si>
   <si>
-    <t>Divisão de Serviços Gerais</t>
+    <t>DIVISÃO DE TRANSPORTE</t>
   </si>
   <si>
     <t>Seção de Requisição de Passagens e Bagagens</t>
   </si>
   <si>
-    <t>Divisão de Controle Patrimonial</t>
-  </si>
-  <si>
-    <t>Assessoria de Comunicação Social</t>
-  </si>
-  <si>
-    <t>SPI</t>
-  </si>
-  <si>
-    <t>Divisão de Intendência</t>
-  </si>
-  <si>
     <t>ASSESSORIA DE COMUNICAÇÃO SOCIAL</t>
   </si>
   <si>
-    <t>DIVISÃO DE TRANSPORTE</t>
+    <t>R$ 3.436.038,50</t>
+  </si>
+  <si>
+    <t>R$ 0,00</t>
+  </si>
+  <si>
+    <t>R$ 3.136.514,46</t>
+  </si>
+  <si>
+    <t>R$ 5.524,00</t>
+  </si>
+  <si>
+    <t>R$ 5.808,00</t>
   </si>
   <si>
     <t>R$ 4.245.297,80</t>
   </si>
   <si>
-    <t>R$ 0,00</t>
+    <t>R$ 968.774,04</t>
+  </si>
+  <si>
+    <t>R$ 25.152.088,87</t>
+  </si>
+  <si>
+    <t>R$ 325.239,20</t>
+  </si>
+  <si>
+    <t>R$ 4.500.025,00</t>
+  </si>
+  <si>
+    <t>R$ 2.138.628,37</t>
+  </si>
+  <si>
+    <t>R$ 1.532,00</t>
+  </si>
+  <si>
+    <t>R$ 1.128.460,00</t>
+  </si>
+  <si>
+    <t>R$ 1.685.509,00</t>
+  </si>
+  <si>
+    <t>R$ 2.500,00</t>
+  </si>
+  <si>
+    <t>R$ 98.850,00</t>
+  </si>
+  <si>
+    <t>R$ 51.515,00</t>
+  </si>
+  <si>
+    <t>R$ 6.747.823,40</t>
+  </si>
+  <si>
+    <t>R$ 3.822.074,00</t>
+  </si>
+  <si>
+    <t>R$ 580.505,00</t>
+  </si>
+  <si>
+    <t>R$ 9.508.413,80</t>
+  </si>
+  <si>
+    <t>R$ 5.880.808,00</t>
+  </si>
+  <si>
+    <t>R$ 1.614.627,00</t>
+  </si>
+  <si>
+    <t>R$ 374.823,00</t>
+  </si>
+  <si>
+    <t>R$ 151.200,00</t>
+  </si>
+  <si>
+    <t>R$ 234.234,00</t>
+  </si>
+  <si>
+    <t>R$ 249.999,00</t>
+  </si>
+  <si>
+    <t>R$ 1.040.000,00</t>
+  </si>
+  <si>
+    <t>R$ 3.916.344,84</t>
+  </si>
+  <si>
+    <t>R$ 3.096.464,64</t>
+  </si>
+  <si>
+    <t>R$ 3.577.824,73</t>
   </si>
   <si>
     <t>R$ 120.768,00</t>
   </si>
   <si>
-    <t>R$ 4.500.025,00</t>
-  </si>
-  <si>
-    <t>R$ 374.823,00</t>
-  </si>
-  <si>
-    <t>R$ 3.916.344,84</t>
-  </si>
-  <si>
-    <t>R$ 2.138.628,37</t>
-  </si>
-  <si>
-    <t>R$ 234.234,00</t>
-  </si>
-  <si>
-    <t>R$ 249.999,00</t>
-  </si>
-  <si>
-    <t>R$ 9.508.413,80</t>
-  </si>
-  <si>
-    <t>R$ 3.096.464,64</t>
-  </si>
-  <si>
-    <t>R$ 1.128.460,00</t>
-  </si>
-  <si>
-    <t>R$ 1.685.509,00</t>
-  </si>
-  <si>
-    <t>R$ 3.436.038,50</t>
-  </si>
-  <si>
-    <t>R$ 325.239,20</t>
-  </si>
-  <si>
-    <t>R$ 1.532,00</t>
-  </si>
-  <si>
-    <t>R$ 151.200,00</t>
-  </si>
-  <si>
-    <t>R$ 3.822.074,00</t>
-  </si>
-  <si>
-    <t>R$ 1.040.000,00</t>
-  </si>
-  <si>
-    <t>R$ 6.747.823,40</t>
-  </si>
-  <si>
-    <t>R$ 25.152.088,87</t>
-  </si>
-  <si>
-    <t>R$ 1.614.627,00</t>
-  </si>
-  <si>
-    <t>R$ 3.577.824,73</t>
+    <t>R$ 3.555.500,00</t>
   </si>
   <si>
     <t>R$ 1.154.163,00</t>
   </si>
   <si>
-    <t>R$ 3.136.514,46</t>
-  </si>
-  <si>
-    <t>R$ 968.774,04</t>
-  </si>
-  <si>
     <t>Sim</t>
   </si>
   <si>
     <t>Não</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1317,46 +1484,43 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F2" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="G2" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="H2" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="J2" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="K2" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="L2" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="M2" t="s">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="N2" t="s">
-        <v>267</v>
-      </c>
-      <c r="O2" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1364,87 +1528,84 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="F3" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="H3" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="J3" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="K3" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="L3" t="s">
-        <v>248</v>
+        <v>294</v>
       </c>
       <c r="N3" t="s">
-        <v>268</v>
-      </c>
-      <c r="O3" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F4" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="G4" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H4" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="J4" t="s">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="K4" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="L4" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="N4" t="s">
-        <v>269</v>
+        <v>315</v>
       </c>
       <c r="O4" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1452,1814 +1613,1766 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F5" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="G5" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="H5" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="J5" t="s">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="K5" t="s">
-        <v>240</v>
+        <v>289</v>
       </c>
       <c r="L5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M5" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="N5" t="s">
-        <v>268</v>
+        <v>316</v>
       </c>
       <c r="O5" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F6" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="G6" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="H6" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="J6" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="K6" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="L6" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
       <c r="N6" t="s">
-        <v>268</v>
-      </c>
-      <c r="O6" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F7" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="G7" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="H7" t="s">
-        <v>182</v>
-      </c>
-      <c r="I7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J7" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="K7" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="L7" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="M7" t="s">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="N7" t="s">
-        <v>268</v>
-      </c>
-      <c r="O7" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F8" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H8" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="J8" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="K8" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="L8" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="M8" t="s">
-        <v>257</v>
+        <v>302</v>
       </c>
       <c r="N8" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
       <c r="O8" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F9" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="G9" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="H9" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="J9" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="K9" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="L9" t="s">
-        <v>249</v>
-      </c>
-      <c r="M9" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="N9" t="s">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="O9" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="F10" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="G10" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H10" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="J10" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="K10" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="L10" t="s">
-        <v>249</v>
-      </c>
-      <c r="M10" t="s">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="N10" t="s">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="O10" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="F11" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H11" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="J11" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="K11" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="L11" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="M11" t="s">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="N11" t="s">
-        <v>268</v>
+        <v>322</v>
       </c>
       <c r="O11" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="G12" t="s">
-        <v>176</v>
+        <v>216</v>
       </c>
       <c r="H12" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="J12" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="K12" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="L12" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="N12" t="s">
-        <v>268</v>
-      </c>
-      <c r="O12" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="G13" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="H13" t="s">
-        <v>188</v>
-      </c>
-      <c r="I13" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="J13" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="K13" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="L13" t="s">
-        <v>247</v>
-      </c>
-      <c r="M13" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="N13" t="s">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="O13" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="P13">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="F14" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H14" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="J14" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="K14" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="L14" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="N14" t="s">
-        <v>270</v>
+        <v>325</v>
+      </c>
+      <c r="O14" t="s">
+        <v>349</v>
       </c>
       <c r="P14">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F15" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H15" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="J15" t="s">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="K15" t="s">
-        <v>242</v>
+        <v>291</v>
       </c>
       <c r="L15" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="N15" t="s">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="O15" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="P15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="E16" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F16" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="H16" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="J16" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="K16" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="L16" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="M16" t="s">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="N16" t="s">
-        <v>272</v>
-      </c>
-      <c r="O16" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="P16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="F17" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="H17" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="J17" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="K17" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="L17" t="s">
-        <v>249</v>
+        <v>294</v>
+      </c>
+      <c r="M17" t="s">
+        <v>303</v>
       </c>
       <c r="N17" t="s">
-        <v>273</v>
-      </c>
-      <c r="O17" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F18" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="H18" t="s">
-        <v>193</v>
-      </c>
-      <c r="I18" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J18" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="K18" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="L18" t="s">
-        <v>249</v>
+        <v>296</v>
+      </c>
+      <c r="M18" t="s">
+        <v>302</v>
       </c>
       <c r="N18" t="s">
-        <v>274</v>
-      </c>
-      <c r="O18" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="P18">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F19" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="H19" t="s">
-        <v>194</v>
-      </c>
-      <c r="I19" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="J19" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="K19" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="L19" t="s">
-        <v>247</v>
+        <v>294</v>
+      </c>
+      <c r="M19" t="s">
+        <v>304</v>
       </c>
       <c r="N19" t="s">
-        <v>275</v>
-      </c>
-      <c r="O19" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="P19">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F20" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="G20" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="H20" t="s">
-        <v>195</v>
-      </c>
-      <c r="I20" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="J20" t="s">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="K20" t="s">
-        <v>242</v>
+        <v>292</v>
       </c>
       <c r="L20" t="s">
-        <v>249</v>
-      </c>
-      <c r="M20" t="s">
-        <v>262</v>
+        <v>299</v>
       </c>
       <c r="N20" t="s">
-        <v>276</v>
-      </c>
-      <c r="O20" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="P20">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E21" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F21" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H21" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
       <c r="I21" t="s">
-        <v>227</v>
+        <v>272</v>
       </c>
       <c r="J21" t="s">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="K21" t="s">
-        <v>242</v>
+        <v>291</v>
       </c>
       <c r="L21" t="s">
-        <v>249</v>
-      </c>
-      <c r="M21" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="N21" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="O21" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P21">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F22" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="H22" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="J22" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="K22" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="L22" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="M22" t="s">
-        <v>254</v>
+        <v>303</v>
       </c>
       <c r="N22" t="s">
-        <v>268</v>
-      </c>
-      <c r="O22" t="s">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="P22">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="E23" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F23" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="H23" t="s">
-        <v>198</v>
+        <v>239</v>
+      </c>
+      <c r="I23" t="s">
+        <v>273</v>
       </c>
       <c r="J23" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
       <c r="K23" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="L23" t="s">
-        <v>250</v>
+        <v>294</v>
+      </c>
+      <c r="M23" t="s">
+        <v>301</v>
       </c>
       <c r="N23" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="O23" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="P23">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E24" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F24" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="H24" t="s">
-        <v>199</v>
-      </c>
-      <c r="I24" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="J24" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="K24" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="L24" t="s">
-        <v>247</v>
-      </c>
-      <c r="M24" t="s">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="N24" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="O24" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="P24">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F25" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="G25" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="H25" t="s">
-        <v>200</v>
-      </c>
-      <c r="I25" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="J25" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="K25" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="L25" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="M25" t="s">
-        <v>262</v>
+        <v>295</v>
       </c>
       <c r="N25" t="s">
-        <v>280</v>
-      </c>
-      <c r="O25" t="s">
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="P25">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F26" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="H26" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="J26" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="K26" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="L26" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="M26" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="N26" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="O26" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="P26">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E27" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F27" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="H27" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="J27" t="s">
-        <v>237</v>
+        <v>280</v>
       </c>
       <c r="K27" t="s">
-        <v>244</v>
+        <v>287</v>
       </c>
       <c r="L27" t="s">
-        <v>251</v>
+        <v>294</v>
+      </c>
+      <c r="M27" t="s">
+        <v>303</v>
       </c>
       <c r="N27" t="s">
-        <v>268</v>
+        <v>336</v>
       </c>
       <c r="O27" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="P27">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F28" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="H28" t="s">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="J28" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="K28" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="L28" t="s">
-        <v>252</v>
-      </c>
-      <c r="M28" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="N28" t="s">
-        <v>268</v>
-      </c>
-      <c r="O28" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="P28">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E29" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="F29" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="H29" t="s">
-        <v>204</v>
+        <v>244</v>
+      </c>
+      <c r="I29" t="s">
+        <v>274</v>
       </c>
       <c r="J29" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="K29" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s">
-        <v>248</v>
+        <v>306</v>
       </c>
       <c r="N29" t="s">
-        <v>281</v>
+        <v>338</v>
       </c>
       <c r="O29" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P29">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="E30" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="F30" t="s">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H30" t="s">
-        <v>205</v>
+        <v>245</v>
+      </c>
+      <c r="I30" t="s">
+        <v>275</v>
       </c>
       <c r="J30" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="K30" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="L30" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
       <c r="N30" t="s">
-        <v>282</v>
+        <v>339</v>
       </c>
       <c r="O30" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P30">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F31" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="G31" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="H31" t="s">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="I31" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="J31" t="s">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="K31" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
       <c r="L31" t="s">
-        <v>251</v>
-      </c>
-      <c r="M31" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="N31" t="s">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="O31" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P31">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F32" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H32" t="s">
-        <v>207</v>
-      </c>
-      <c r="I32" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="J32" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="K32" t="s">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="L32" t="s">
-        <v>250</v>
+        <v>299</v>
       </c>
       <c r="N32" t="s">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="O32" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P32">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F33" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="G33" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H33" t="s">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="J33" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="K33" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="L33" t="s">
-        <v>252</v>
+        <v>294</v>
+      </c>
+      <c r="M33" t="s">
+        <v>307</v>
       </c>
       <c r="N33" t="s">
-        <v>285</v>
+        <v>342</v>
       </c>
       <c r="O33" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="P33">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F34" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="G34" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H34" t="s">
-        <v>209</v>
+        <v>249</v>
+      </c>
+      <c r="I34" t="s">
+        <v>277</v>
       </c>
       <c r="J34" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="K34" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="L34" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s">
-        <v>268</v>
+        <v>343</v>
       </c>
       <c r="O34" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="P34">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E35" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F35" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="G35" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="H35" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="J35" t="s">
-        <v>239</v>
+        <v>282</v>
       </c>
       <c r="K35" t="s">
-        <v>246</v>
+        <v>289</v>
       </c>
       <c r="L35" t="s">
-        <v>253</v>
+        <v>296</v>
+      </c>
+      <c r="M35" t="s">
+        <v>302</v>
       </c>
       <c r="N35" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="O35" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="P35">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="E36" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F36" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="G36" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H36" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
       <c r="J36" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="K36" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="L36" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s">
-        <v>252</v>
+        <v>308</v>
       </c>
       <c r="N36" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="O36" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="P36">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="E37" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F37" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="G37" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="H37" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="J37" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="K37" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="L37" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="N37" t="s">
-        <v>286</v>
-      </c>
-      <c r="O37" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="P37">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D38" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="E38" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="F38" t="s">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="G38" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="H38" t="s">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="J38" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="K38" t="s">
-        <v>240</v>
+        <v>293</v>
       </c>
       <c r="L38" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="N38" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="O38" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P38">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D39" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="E39" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F39" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="G39" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="H39" t="s">
-        <v>214</v>
+        <v>254</v>
       </c>
       <c r="J39" t="s">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="K39" t="s">
-        <v>242</v>
+        <v>292</v>
       </c>
       <c r="L39" t="s">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="M39" t="s">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="N39" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="O39" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="P39">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D40" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E40" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F40" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="G40" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H40" t="s">
-        <v>215</v>
+        <v>255</v>
       </c>
       <c r="I40" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="J40" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="K40" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="L40" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
       <c r="M40" t="s">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="N40" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="O40" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="P40">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E41" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F41" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="G41" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H41" t="s">
-        <v>216</v>
+        <v>256</v>
       </c>
       <c r="J41" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="K41" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="L41" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="M41" t="s">
-        <v>254</v>
+        <v>309</v>
       </c>
       <c r="N41" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="O41" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="P41">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D42" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E42" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F42" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="G42" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="H42" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="J42" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="K42" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="L42" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
       <c r="M42" t="s">
-        <v>256</v>
+        <v>310</v>
       </c>
       <c r="N42" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="O42" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="P42">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E43" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F43" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="G43" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H43" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="J43" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="K43" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="L43" t="s">
-        <v>249</v>
+        <v>296</v>
+      </c>
+      <c r="M43" t="s">
+        <v>302</v>
       </c>
       <c r="N43" t="s">
-        <v>290</v>
+        <v>344</v>
       </c>
       <c r="O43" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="P43">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3267,43 +3380,43 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E44" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F44" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="G44" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H44" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="J44" t="s">
-        <v>233</v>
+        <v>285</v>
       </c>
       <c r="K44" t="s">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="L44" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="M44" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="N44" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="O44" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="P44">
         <v>10</v>
@@ -3314,40 +3427,40 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D45" t="s">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="E45" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F45" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="G45" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H45" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J45" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="K45" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="L45" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="N45" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="O45" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P45">
         <v>10</v>
@@ -3358,43 +3471,40 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="E46" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F46" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="G46" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="H46" t="s">
-        <v>219</v>
-      </c>
-      <c r="I46" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="J46" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="K46" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="L46" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="N46" t="s">
-        <v>268</v>
+        <v>345</v>
       </c>
       <c r="O46" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P46">
         <v>10</v>
@@ -3405,40 +3515,40 @@
         <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D47" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="E47" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F47" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="G47" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="H47" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="J47" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="K47" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="L47" t="s">
-        <v>249</v>
+        <v>294</v>
+      </c>
+      <c r="M47" t="s">
+        <v>311</v>
       </c>
       <c r="N47" t="s">
-        <v>292</v>
-      </c>
-      <c r="O47" t="s">
-        <v>294</v>
+        <v>346</v>
       </c>
       <c r="P47">
         <v>10</v>
@@ -3449,43 +3559,46 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D48" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="E48" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="G48" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="H48" t="s">
-        <v>220</v>
+        <v>263</v>
+      </c>
+      <c r="I48" t="s">
+        <v>263</v>
       </c>
       <c r="J48" t="s">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="K48" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
       <c r="L48" t="s">
-        <v>251</v>
+        <v>296</v>
       </c>
       <c r="M48" t="s">
-        <v>251</v>
+        <v>312</v>
       </c>
       <c r="N48" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="O48" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="P48">
         <v>10</v>
@@ -3493,90 +3606,967 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D49" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="E49" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F49" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="G49" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="H49" t="s">
-        <v>221</v>
+        <v>264</v>
+      </c>
+      <c r="I49" t="s">
+        <v>264</v>
       </c>
       <c r="J49" t="s">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="K49" t="s">
-        <v>242</v>
+        <v>291</v>
       </c>
       <c r="L49" t="s">
-        <v>249</v>
-      </c>
-      <c r="M49" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="N49" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="O49" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="P49">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B50" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" t="s">
+        <v>142</v>
+      </c>
+      <c r="E50" t="s">
+        <v>163</v>
+      </c>
+      <c r="F50" t="s">
+        <v>211</v>
+      </c>
+      <c r="G50" t="s">
+        <v>216</v>
+      </c>
+      <c r="H50" t="s">
+        <v>243</v>
+      </c>
+      <c r="J50" t="s">
+        <v>280</v>
+      </c>
+      <c r="K50" t="s">
+        <v>287</v>
+      </c>
+      <c r="L50" t="s">
+        <v>294</v>
+      </c>
+      <c r="N50" t="s">
+        <v>347</v>
+      </c>
+      <c r="O50" t="s">
+        <v>349</v>
+      </c>
+      <c r="P50">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" t="s">
         <v>74</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" t="s">
+        <v>163</v>
+      </c>
+      <c r="F51" t="s">
+        <v>212</v>
+      </c>
+      <c r="G51" t="s">
+        <v>217</v>
+      </c>
+      <c r="H51" t="s">
+        <v>265</v>
+      </c>
+      <c r="J51" t="s">
+        <v>282</v>
+      </c>
+      <c r="K51" t="s">
+        <v>289</v>
+      </c>
+      <c r="L51" t="s">
+        <v>296</v>
+      </c>
+      <c r="P51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" t="s">
         <v>75</v>
       </c>
-      <c r="D50" t="s">
-        <v>124</v>
-      </c>
-      <c r="E50" t="s">
-        <v>125</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="C52" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" t="s">
+        <v>163</v>
+      </c>
+      <c r="G52" t="s">
+        <v>217</v>
+      </c>
+      <c r="J52" t="s">
+        <v>282</v>
+      </c>
+      <c r="K52" t="s">
+        <v>289</v>
+      </c>
+      <c r="L52" t="s">
+        <v>296</v>
+      </c>
+      <c r="P52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" t="s">
+        <v>163</v>
+      </c>
+      <c r="F53" t="s">
+        <v>169</v>
+      </c>
+      <c r="G53" t="s">
+        <v>217</v>
+      </c>
+      <c r="H53" t="s">
+        <v>223</v>
+      </c>
+      <c r="J53" t="s">
+        <v>280</v>
+      </c>
+      <c r="K53" t="s">
+        <v>287</v>
+      </c>
+      <c r="L53" t="s">
+        <v>294</v>
+      </c>
+      <c r="P53">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" t="s">
+        <v>77</v>
+      </c>
+      <c r="C54" t="s">
+        <v>94</v>
+      </c>
+      <c r="D54" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" t="s">
+        <v>163</v>
+      </c>
+      <c r="F54" t="s">
+        <v>169</v>
+      </c>
+      <c r="G54" t="s">
+        <v>217</v>
+      </c>
+      <c r="H54" t="s">
+        <v>223</v>
+      </c>
+      <c r="J54" t="s">
+        <v>280</v>
+      </c>
+      <c r="K54" t="s">
+        <v>287</v>
+      </c>
+      <c r="L54" t="s">
+        <v>294</v>
+      </c>
+      <c r="N54" t="s">
+        <v>317</v>
+      </c>
+      <c r="P54">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B55" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55" t="s">
+        <v>163</v>
+      </c>
+      <c r="F55" t="s">
+        <v>171</v>
+      </c>
+      <c r="G55" t="s">
+        <v>217</v>
+      </c>
+      <c r="H55" t="s">
+        <v>225</v>
+      </c>
+      <c r="J55" t="s">
+        <v>282</v>
+      </c>
+      <c r="K55" t="s">
+        <v>289</v>
+      </c>
+      <c r="L55" t="s">
+        <v>296</v>
+      </c>
+      <c r="N55" t="s">
+        <v>319</v>
+      </c>
+      <c r="O55" t="s">
+        <v>348</v>
+      </c>
+      <c r="P55">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" t="s">
+        <v>148</v>
+      </c>
+      <c r="E56" t="s">
+        <v>165</v>
+      </c>
+      <c r="F56" t="s">
         <v>173</v>
       </c>
-      <c r="G50" t="s">
-        <v>175</v>
-      </c>
-      <c r="H50" t="s">
-        <v>222</v>
-      </c>
-      <c r="J50" t="s">
-        <v>235</v>
-      </c>
-      <c r="K50" t="s">
-        <v>242</v>
-      </c>
-      <c r="L50" t="s">
-        <v>249</v>
-      </c>
-      <c r="N50" t="s">
+      <c r="G56" t="s">
+        <v>217</v>
+      </c>
+      <c r="H56" t="s">
+        <v>227</v>
+      </c>
+      <c r="J56" t="s">
+        <v>282</v>
+      </c>
+      <c r="K56" t="s">
+        <v>289</v>
+      </c>
+      <c r="L56" t="s">
+        <v>296</v>
+      </c>
+      <c r="N56" t="s">
+        <v>321</v>
+      </c>
+      <c r="O56" t="s">
+        <v>349</v>
+      </c>
+      <c r="P56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57" t="s">
+        <v>23</v>
+      </c>
+      <c r="B57" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" t="s">
+        <v>149</v>
+      </c>
+      <c r="E57" t="s">
+        <v>163</v>
+      </c>
+      <c r="F57" t="s">
+        <v>171</v>
+      </c>
+      <c r="G57" t="s">
+        <v>217</v>
+      </c>
+      <c r="H57" t="s">
+        <v>225</v>
+      </c>
+      <c r="J57" t="s">
+        <v>282</v>
+      </c>
+      <c r="K57" t="s">
+        <v>289</v>
+      </c>
+      <c r="L57" t="s">
+        <v>296</v>
+      </c>
+      <c r="N57" t="s">
+        <v>319</v>
+      </c>
+      <c r="O57" t="s">
+        <v>348</v>
+      </c>
+      <c r="P57">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58" t="s">
+        <v>23</v>
+      </c>
+      <c r="B58" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" t="s">
+        <v>94</v>
+      </c>
+      <c r="D58" t="s">
+        <v>150</v>
+      </c>
+      <c r="E58" t="s">
+        <v>163</v>
+      </c>
+      <c r="F58" t="s">
+        <v>169</v>
+      </c>
+      <c r="G58" t="s">
+        <v>217</v>
+      </c>
+      <c r="H58" t="s">
+        <v>223</v>
+      </c>
+      <c r="J58" t="s">
+        <v>280</v>
+      </c>
+      <c r="K58" t="s">
+        <v>287</v>
+      </c>
+      <c r="L58" t="s">
+        <v>294</v>
+      </c>
+      <c r="N58" t="s">
+        <v>317</v>
+      </c>
+      <c r="P58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59" t="s">
+        <v>23</v>
+      </c>
+      <c r="B59" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" t="s">
+        <v>151</v>
+      </c>
+      <c r="E59" t="s">
+        <v>163</v>
+      </c>
+      <c r="F59" t="s">
+        <v>182</v>
+      </c>
+      <c r="G59" t="s">
+        <v>217</v>
+      </c>
+      <c r="H59" t="s">
+        <v>266</v>
+      </c>
+      <c r="I59" t="s">
+        <v>272</v>
+      </c>
+      <c r="J59" t="s">
+        <v>284</v>
+      </c>
+      <c r="K59" t="s">
+        <v>291</v>
+      </c>
+      <c r="L59" t="s">
+        <v>298</v>
+      </c>
+      <c r="N59" t="s">
+        <v>332</v>
+      </c>
+      <c r="O59" t="s">
+        <v>349</v>
+      </c>
+      <c r="P59">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" t="s">
+        <v>152</v>
+      </c>
+      <c r="E60" t="s">
+        <v>163</v>
+      </c>
+      <c r="F60" t="s">
+        <v>184</v>
+      </c>
+      <c r="G60" t="s">
+        <v>217</v>
+      </c>
+      <c r="H60" t="s">
+        <v>239</v>
+      </c>
+      <c r="I60" t="s">
+        <v>273</v>
+      </c>
+      <c r="J60" t="s">
+        <v>280</v>
+      </c>
+      <c r="K60" t="s">
+        <v>287</v>
+      </c>
+      <c r="L60" t="s">
+        <v>294</v>
+      </c>
+      <c r="N60" t="s">
+        <v>334</v>
+      </c>
+      <c r="O60" t="s">
+        <v>348</v>
+      </c>
+      <c r="P60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B61" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" t="s">
+        <v>153</v>
+      </c>
+      <c r="E61" t="s">
+        <v>163</v>
+      </c>
+      <c r="F61" t="s">
+        <v>184</v>
+      </c>
+      <c r="G61" t="s">
+        <v>217</v>
+      </c>
+      <c r="H61" t="s">
+        <v>239</v>
+      </c>
+      <c r="I61" t="s">
+        <v>273</v>
+      </c>
+      <c r="J61" t="s">
+        <v>280</v>
+      </c>
+      <c r="K61" t="s">
+        <v>287</v>
+      </c>
+      <c r="L61" t="s">
+        <v>294</v>
+      </c>
+      <c r="N61" t="s">
+        <v>334</v>
+      </c>
+      <c r="O61" t="s">
+        <v>348</v>
+      </c>
+      <c r="P61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
+      <c r="A62" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" t="s">
+        <v>154</v>
+      </c>
+      <c r="E62" t="s">
+        <v>163</v>
+      </c>
+      <c r="F62" t="s">
+        <v>184</v>
+      </c>
+      <c r="G62" t="s">
+        <v>217</v>
+      </c>
+      <c r="H62" t="s">
+        <v>239</v>
+      </c>
+      <c r="I62" t="s">
+        <v>273</v>
+      </c>
+      <c r="J62" t="s">
+        <v>280</v>
+      </c>
+      <c r="K62" t="s">
+        <v>287</v>
+      </c>
+      <c r="L62" t="s">
+        <v>294</v>
+      </c>
+      <c r="N62" t="s">
+        <v>334</v>
+      </c>
+      <c r="O62" t="s">
+        <v>348</v>
+      </c>
+      <c r="P62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
+      <c r="A63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" t="s">
+        <v>94</v>
+      </c>
+      <c r="D63" t="s">
+        <v>155</v>
+      </c>
+      <c r="E63" t="s">
+        <v>163</v>
+      </c>
+      <c r="F63" t="s">
+        <v>184</v>
+      </c>
+      <c r="G63" t="s">
+        <v>217</v>
+      </c>
+      <c r="H63" t="s">
+        <v>239</v>
+      </c>
+      <c r="I63" t="s">
+        <v>273</v>
+      </c>
+      <c r="J63" t="s">
+        <v>280</v>
+      </c>
+      <c r="K63" t="s">
+        <v>287</v>
+      </c>
+      <c r="L63" t="s">
+        <v>294</v>
+      </c>
+      <c r="N63" t="s">
+        <v>334</v>
+      </c>
+      <c r="O63" t="s">
+        <v>348</v>
+      </c>
+      <c r="P63">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
+      <c r="A64" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64" t="s">
+        <v>156</v>
+      </c>
+      <c r="E64" t="s">
+        <v>163</v>
+      </c>
+      <c r="F64" t="s">
+        <v>184</v>
+      </c>
+      <c r="G64" t="s">
+        <v>217</v>
+      </c>
+      <c r="H64" t="s">
+        <v>239</v>
+      </c>
+      <c r="I64" t="s">
+        <v>273</v>
+      </c>
+      <c r="J64" t="s">
+        <v>280</v>
+      </c>
+      <c r="K64" t="s">
+        <v>287</v>
+      </c>
+      <c r="L64" t="s">
+        <v>294</v>
+      </c>
+      <c r="N64" t="s">
+        <v>334</v>
+      </c>
+      <c r="O64" t="s">
+        <v>348</v>
+      </c>
+      <c r="P64">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
+      <c r="A65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" t="s">
+        <v>94</v>
+      </c>
+      <c r="D65" t="s">
+        <v>157</v>
+      </c>
+      <c r="E65" t="s">
+        <v>163</v>
+      </c>
+      <c r="F65" t="s">
+        <v>184</v>
+      </c>
+      <c r="G65" t="s">
+        <v>217</v>
+      </c>
+      <c r="H65" t="s">
+        <v>239</v>
+      </c>
+      <c r="I65" t="s">
+        <v>273</v>
+      </c>
+      <c r="J65" t="s">
+        <v>280</v>
+      </c>
+      <c r="K65" t="s">
+        <v>287</v>
+      </c>
+      <c r="L65" t="s">
+        <v>294</v>
+      </c>
+      <c r="N65" t="s">
+        <v>334</v>
+      </c>
+      <c r="O65" t="s">
+        <v>348</v>
+      </c>
+      <c r="P65">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" t="s">
+        <v>23</v>
+      </c>
+      <c r="B66" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" t="s">
+        <v>94</v>
+      </c>
+      <c r="D66" t="s">
+        <v>158</v>
+      </c>
+      <c r="E66" t="s">
+        <v>163</v>
+      </c>
+      <c r="F66" t="s">
+        <v>170</v>
+      </c>
+      <c r="G66" t="s">
+        <v>217</v>
+      </c>
+      <c r="H66" t="s">
+        <v>267</v>
+      </c>
+      <c r="J66" t="s">
+        <v>282</v>
+      </c>
+      <c r="K66" t="s">
+        <v>289</v>
+      </c>
+      <c r="L66" t="s">
+        <v>296</v>
+      </c>
+      <c r="N66" t="s">
+        <v>318</v>
+      </c>
+      <c r="P66">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" t="s">
+        <v>23</v>
+      </c>
+      <c r="B67" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67" t="s">
+        <v>159</v>
+      </c>
+      <c r="E67" t="s">
+        <v>164</v>
+      </c>
+      <c r="F67" t="s">
+        <v>208</v>
+      </c>
+      <c r="G67" t="s">
+        <v>215</v>
+      </c>
+      <c r="H67" t="s">
         <v>268</v>
       </c>
-      <c r="P50">
-        <v>12</v>
+      <c r="J67" t="s">
+        <v>280</v>
+      </c>
+      <c r="K67" t="s">
+        <v>287</v>
+      </c>
+      <c r="L67" t="s">
+        <v>294</v>
+      </c>
+      <c r="N67" t="s">
+        <v>315</v>
+      </c>
+      <c r="O67" t="s">
+        <v>349</v>
+      </c>
+      <c r="P67">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" t="s">
+        <v>23</v>
+      </c>
+      <c r="B68" t="s">
+        <v>91</v>
+      </c>
+      <c r="C68" t="s">
+        <v>94</v>
+      </c>
+      <c r="D68" t="s">
+        <v>160</v>
+      </c>
+      <c r="E68" t="s">
+        <v>164</v>
+      </c>
+      <c r="F68" t="s">
+        <v>213</v>
+      </c>
+      <c r="G68" t="s">
+        <v>217</v>
+      </c>
+      <c r="H68" t="s">
+        <v>269</v>
+      </c>
+      <c r="J68" t="s">
+        <v>282</v>
+      </c>
+      <c r="K68" t="s">
+        <v>289</v>
+      </c>
+      <c r="L68" t="s">
+        <v>296</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68" t="s">
+        <v>350</v>
+      </c>
+      <c r="P68">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69" t="s">
+        <v>23</v>
+      </c>
+      <c r="B69" t="s">
+        <v>92</v>
+      </c>
+      <c r="C69" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" t="s">
+        <v>161</v>
+      </c>
+      <c r="E69" t="s">
+        <v>164</v>
+      </c>
+      <c r="F69" t="s">
+        <v>176</v>
+      </c>
+      <c r="G69" t="s">
+        <v>217</v>
+      </c>
+      <c r="H69" t="s">
+        <v>270</v>
+      </c>
+      <c r="J69" t="s">
+        <v>284</v>
+      </c>
+      <c r="K69" t="s">
+        <v>291</v>
+      </c>
+      <c r="L69" t="s">
+        <v>298</v>
+      </c>
+      <c r="N69" t="s">
+        <v>326</v>
+      </c>
+      <c r="O69" t="s">
+        <v>349</v>
+      </c>
+      <c r="P69">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" t="s">
+        <v>93</v>
+      </c>
+      <c r="C70" t="s">
+        <v>94</v>
+      </c>
+      <c r="D70" t="s">
+        <v>162</v>
+      </c>
+      <c r="E70" t="s">
+        <v>163</v>
+      </c>
+      <c r="F70" t="s">
+        <v>214</v>
+      </c>
+      <c r="G70" t="s">
+        <v>216</v>
+      </c>
+      <c r="H70" t="s">
+        <v>271</v>
+      </c>
+      <c r="I70" t="s">
+        <v>279</v>
+      </c>
+      <c r="J70" t="s">
+        <v>280</v>
+      </c>
+      <c r="K70" t="s">
+        <v>287</v>
+      </c>
+      <c r="L70" t="s">
+        <v>294</v>
+      </c>
+      <c r="M70" t="s">
+        <v>313</v>
+      </c>
+      <c r="N70" t="s">
+        <v>315</v>
+      </c>
+      <c r="O70" t="s">
+        <v>348</v>
+      </c>
+      <c r="P70">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
